--- a/gu_in/ItemTimer.edf/TimerItem.xlsx
+++ b/gu_in/ItemTimer.edf/TimerItem.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EE6C50F-73C8-4746-8C4C-DA41154124C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA5F3A2E-0B58-4DE7-BBA9-1EE6A28A0FD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TimerItem" sheetId="1" r:id="rId1"/>
@@ -2065,15 +2065,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E561"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2090,7 +2090,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2104,7 +2104,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="str">
         <f>"t"&amp;B3</f>
         <v>tircsa05</v>
@@ -2119,7 +2119,7 @@
         <v>86400</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="str">
         <f t="shared" ref="A4:A67" si="0">"t"&amp;B4</f>
         <v>tircsa06</v>
@@ -2134,7 +2134,7 @@
         <v>518400</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="str">
         <f t="shared" si="0"/>
         <v>tircsa07</v>
@@ -2149,7 +2149,7 @@
         <v>1209600</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="str">
         <f t="shared" si="0"/>
         <v>tircsa08</v>
@@ -2164,7 +2164,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="str">
         <f t="shared" si="0"/>
         <v>tircsa09</v>
@@ -2179,7 +2179,7 @@
         <v>172800</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="str">
         <f t="shared" si="0"/>
         <v>tircsa10</v>
@@ -2194,7 +2194,7 @@
         <v>518400</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="str">
         <f t="shared" si="0"/>
         <v>tircsa11</v>
@@ -2209,7 +2209,7 @@
         <v>1209600</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="str">
         <f t="shared" si="0"/>
         <v>tircsa12</v>
@@ -2224,7 +2224,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="str">
         <f t="shared" si="0"/>
         <v>tirbud01</v>
@@ -2239,7 +2239,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="str">
         <f t="shared" si="0"/>
         <v>tirbud02</v>
@@ -2254,7 +2254,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="str">
         <f t="shared" si="0"/>
         <v>tirbud03</v>
@@ -2269,7 +2269,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="str">
         <f t="shared" si="0"/>
         <v>tirbud04</v>
@@ -2284,7 +2284,7 @@
         <v>3600</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="str">
         <f t="shared" si="0"/>
         <v>tirbud05</v>
@@ -2299,7 +2299,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="str">
         <f t="shared" si="0"/>
         <v>tirbud06</v>
@@ -2314,7 +2314,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="str">
         <f t="shared" si="0"/>
         <v>tirbud07</v>
@@ -2329,7 +2329,7 @@
         <v>3600</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="str">
         <f t="shared" si="0"/>
         <v>tircsa13</v>
@@ -2344,7 +2344,7 @@
         <v>21600</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="str">
         <f t="shared" si="0"/>
         <v>tircsa14</v>
@@ -2359,7 +2359,7 @@
         <v>43200</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="str">
         <f t="shared" si="0"/>
         <v>tircsa15</v>
@@ -2374,7 +2374,7 @@
         <v>72000</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="str">
         <f t="shared" si="0"/>
         <v>tircsa16</v>
@@ -2389,7 +2389,7 @@
         <v>108000</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="str">
         <f t="shared" si="0"/>
         <v>tircsa17</v>
@@ -2404,7 +2404,7 @@
         <v>21600</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="str">
         <f t="shared" si="0"/>
         <v>tircsa18</v>
@@ -2419,7 +2419,7 @@
         <v>43200</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="str">
         <f t="shared" si="0"/>
         <v>tircsa19</v>
@@ -2434,7 +2434,7 @@
         <v>72000</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="str">
         <f t="shared" si="0"/>
         <v>tircsa20</v>
@@ -2449,7 +2449,7 @@
         <v>108000</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="str">
         <f t="shared" si="0"/>
         <v>tircsa21</v>
@@ -2464,7 +2464,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="str">
         <f t="shared" si="0"/>
         <v>tircsa22</v>
@@ -2479,7 +2479,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="str">
         <f t="shared" si="0"/>
         <v>tircsa23</v>
@@ -2494,7 +2494,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="str">
         <f t="shared" si="0"/>
         <v>tcucou00</v>
@@ -2509,7 +2509,7 @@
         <v>86400</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="str">
         <f t="shared" si="0"/>
         <v>tcucou01</v>
@@ -2524,7 +2524,7 @@
         <v>86400</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="str">
         <f t="shared" si="0"/>
         <v>tcucou02</v>
@@ -2539,7 +2539,7 @@
         <v>86400</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="str">
         <f t="shared" si="0"/>
         <v>tcucou03</v>
@@ -2554,7 +2554,7 @@
         <v>86400</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="str">
         <f t="shared" si="0"/>
         <v>tcucou04</v>
@@ -2569,7 +2569,7 @@
         <v>86400</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="str">
         <f t="shared" si="0"/>
         <v>tcucou05</v>
@@ -2584,7 +2584,7 @@
         <v>86400</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="str">
         <f t="shared" si="0"/>
         <v>tcucou06</v>
@@ -2599,7 +2599,7 @@
         <v>86400</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="str">
         <f t="shared" si="0"/>
         <v>tcucou07</v>
@@ -2614,7 +2614,7 @@
         <v>86400</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="str">
         <f t="shared" si="0"/>
         <v>tcucou08</v>
@@ -2629,7 +2629,7 @@
         <v>86400</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="str">
         <f t="shared" si="0"/>
         <v>tcucou09</v>
@@ -2644,7 +2644,7 @@
         <v>86400</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="str">
         <f t="shared" si="0"/>
         <v>tcucou10</v>
@@ -2659,7 +2659,7 @@
         <v>86400</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="str">
         <f t="shared" si="0"/>
         <v>tiabbd16</v>
@@ -2674,7 +2674,7 @@
         <v>21600</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="str">
         <f t="shared" si="0"/>
         <v>tiabbd17</v>
@@ -2689,7 +2689,7 @@
         <v>21600</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="str">
         <f t="shared" si="0"/>
         <v>tiabbd18</v>
@@ -2704,7 +2704,7 @@
         <v>21600</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="str">
         <f t="shared" si="0"/>
         <v>tiabbd19</v>
@@ -2719,7 +2719,7 @@
         <v>21600</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="str">
         <f t="shared" si="0"/>
         <v>tiabbd20</v>
@@ -2734,7 +2734,7 @@
         <v>21600</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="str">
         <f t="shared" si="0"/>
         <v>tiabbd21</v>
@@ -2749,7 +2749,7 @@
         <v>21600</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="str">
         <f t="shared" si="0"/>
         <v>tiaccd81</v>
@@ -2764,7 +2764,7 @@
         <v>21600</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="str">
         <f t="shared" si="0"/>
         <v>tiaccd82</v>
@@ -2779,7 +2779,7 @@
         <v>21600</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="str">
         <f t="shared" si="0"/>
         <v>tiaccd83</v>
@@ -2794,7 +2794,7 @@
         <v>21600</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="str">
         <f t="shared" si="0"/>
         <v>tiaaad56</v>
@@ -2809,7 +2809,7 @@
         <v>21600</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="str">
         <f t="shared" si="0"/>
         <v>tiaaad57</v>
@@ -2824,7 +2824,7 @@
         <v>21600</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="str">
         <f t="shared" si="0"/>
         <v>tiaaad58</v>
@@ -2839,7 +2839,7 @@
         <v>21600</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="str">
         <f t="shared" si="0"/>
         <v>tiibbd81</v>
@@ -2854,7 +2854,7 @@
         <v>21600</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="str">
         <f t="shared" si="0"/>
         <v>tiibbd82</v>
@@ -2869,7 +2869,7 @@
         <v>21600</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="str">
         <f t="shared" si="0"/>
         <v>tiibbd83</v>
@@ -2884,7 +2884,7 @@
         <v>21600</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="str">
         <f t="shared" si="0"/>
         <v>tiiccd16</v>
@@ -2899,7 +2899,7 @@
         <v>21600</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="str">
         <f t="shared" si="0"/>
         <v>tiiccd17</v>
@@ -2914,7 +2914,7 @@
         <v>21600</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="str">
         <f t="shared" si="0"/>
         <v>tiiccd18</v>
@@ -2929,7 +2929,7 @@
         <v>21600</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="str">
         <f t="shared" si="0"/>
         <v>tiiccd19</v>
@@ -2944,7 +2944,7 @@
         <v>21600</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="str">
         <f t="shared" si="0"/>
         <v>tiiccd20</v>
@@ -2959,7 +2959,7 @@
         <v>21600</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="str">
         <f t="shared" si="0"/>
         <v>tiiccd21</v>
@@ -2974,7 +2974,7 @@
         <v>21600</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="str">
         <f t="shared" si="0"/>
         <v>tiiaad81</v>
@@ -2989,7 +2989,7 @@
         <v>21600</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="str">
         <f t="shared" si="0"/>
         <v>tiiaad82</v>
@@ -3004,7 +3004,7 @@
         <v>21600</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="str">
         <f t="shared" si="0"/>
         <v>tiiaad83</v>
@@ -3019,7 +3019,7 @@
         <v>21600</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="str">
         <f t="shared" si="0"/>
         <v>tirsry01</v>
@@ -3034,7 +3034,7 @@
         <v>172800</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="str">
         <f t="shared" si="0"/>
         <v>tirwav01</v>
@@ -3049,7 +3049,7 @@
         <v>5400</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="str">
         <f t="shared" si="0"/>
         <v>tiwkho55</v>
@@ -3064,7 +3064,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="str">
         <f t="shared" si="0"/>
         <v>tiwbho55</v>
@@ -3079,7 +3079,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="str">
         <f t="shared" ref="A68:A131" si="1">"t"&amp;B68</f>
         <v>tiwtho55</v>
@@ -3094,7 +3094,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="str">
         <f t="shared" si="1"/>
         <v>tiwmkn55</v>
@@ -3109,7 +3109,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="str">
         <f t="shared" si="1"/>
         <v>tiwmsh55</v>
@@ -3124,7 +3124,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="str">
         <f t="shared" si="1"/>
         <v>tiwmbh55</v>
@@ -3139,7 +3139,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="str">
         <f t="shared" si="1"/>
         <v>tiwmfh55</v>
@@ -3154,7 +3154,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="str">
         <f t="shared" si="1"/>
         <v>tidmsb55</v>
@@ -3169,7 +3169,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="str">
         <f t="shared" si="1"/>
         <v>tidesb55</v>
@@ -3184,7 +3184,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="str">
         <f t="shared" si="1"/>
         <v>tipexp01</v>
@@ -3199,7 +3199,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="str">
         <f t="shared" si="1"/>
         <v>tipexp03</v>
@@ -3214,7 +3214,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="str">
         <f t="shared" si="1"/>
         <v>tircsa24</v>
@@ -3229,7 +3229,7 @@
         <v>172800</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="str">
         <f t="shared" si="1"/>
         <v>tircsa25</v>
@@ -3244,7 +3244,7 @@
         <v>172800</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="str">
         <f t="shared" si="1"/>
         <v>tircsa26</v>
@@ -3259,7 +3259,7 @@
         <v>604800</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="str">
         <f t="shared" si="1"/>
         <v>tircsa27</v>
@@ -3274,7 +3274,7 @@
         <v>604800</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="str">
         <f t="shared" si="1"/>
         <v>tircsa28</v>
@@ -3289,7 +3289,7 @@
         <v>172800</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="str">
         <f t="shared" si="1"/>
         <v>tircsa29</v>
@@ -3304,7 +3304,7 @@
         <v>172800</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="str">
         <f t="shared" si="1"/>
         <v>tircsa30</v>
@@ -3319,7 +3319,7 @@
         <v>604800</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="str">
         <f t="shared" si="1"/>
         <v>tircsa31</v>
@@ -3334,7 +3334,7 @@
         <v>172800</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="str">
         <f t="shared" si="1"/>
         <v>tircsa32</v>
@@ -3349,7 +3349,7 @@
         <v>172800</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="str">
         <f t="shared" si="1"/>
         <v>tircsa33</v>
@@ -3364,7 +3364,7 @@
         <v>604800</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="str">
         <f t="shared" si="1"/>
         <v>tircsa34</v>
@@ -3379,7 +3379,7 @@
         <v>604800</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="str">
         <f t="shared" si="1"/>
         <v>tircsa35</v>
@@ -3394,7 +3394,7 @@
         <v>604800</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="str">
         <f t="shared" si="1"/>
         <v>tircsa36</v>
@@ -3409,7 +3409,7 @@
         <v>604800</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="str">
         <f t="shared" si="1"/>
         <v>tircsa37</v>
@@ -3424,7 +3424,7 @@
         <v>604800</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="str">
         <f t="shared" si="1"/>
         <v>tircsa38</v>
@@ -3439,7 +3439,7 @@
         <v>172800</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="str">
         <f t="shared" si="1"/>
         <v>tircsa39</v>
@@ -3454,7 +3454,7 @@
         <v>604800</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="str">
         <f t="shared" si="1"/>
         <v>tircsa40</v>
@@ -3469,7 +3469,7 @@
         <v>604800</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="str">
         <f t="shared" si="1"/>
         <v>tircsa41</v>
@@ -3484,7 +3484,7 @@
         <v>604800</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="str">
         <f t="shared" si="1"/>
         <v>tircsa42</v>
@@ -3499,7 +3499,7 @@
         <v>604800</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="str">
         <f t="shared" si="1"/>
         <v>tirchm01</v>
@@ -3514,7 +3514,7 @@
         <v>432000</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="str">
         <f t="shared" si="1"/>
         <v>tirchm02</v>
@@ -3529,7 +3529,7 @@
         <v>432000</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="str">
         <f t="shared" si="1"/>
         <v>tirchm03</v>
@@ -3544,7 +3544,7 @@
         <v>432000</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="str">
         <f t="shared" si="1"/>
         <v>tirchm04</v>
@@ -3559,7 +3559,7 @@
         <v>432000</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="str">
         <f t="shared" si="1"/>
         <v>tirchm05</v>
@@ -3574,7 +3574,7 @@
         <v>432000</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="str">
         <f t="shared" si="1"/>
         <v>tirchm06</v>
@@ -3589,7 +3589,7 @@
         <v>432000</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="str">
         <f t="shared" si="1"/>
         <v>tirchm07</v>
@@ -3604,7 +3604,7 @@
         <v>432000</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="str">
         <f t="shared" si="1"/>
         <v>tirchm08</v>
@@ -3619,7 +3619,7 @@
         <v>432000</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="str">
         <f t="shared" si="1"/>
         <v>tirchm09</v>
@@ -3634,7 +3634,7 @@
         <v>432000</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="str">
         <f t="shared" si="1"/>
         <v>tirchm10</v>
@@ -3649,7 +3649,7 @@
         <v>432000</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="str">
         <f t="shared" si="1"/>
         <v>tirchm11</v>
@@ -3664,7 +3664,7 @@
         <v>432000</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="str">
         <f t="shared" si="1"/>
         <v>tirchm12</v>
@@ -3679,7 +3679,7 @@
         <v>432000</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="str">
         <f t="shared" si="1"/>
         <v>tirchm13</v>
@@ -3694,7 +3694,7 @@
         <v>432000</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="str">
         <f t="shared" si="1"/>
         <v>tirchm14</v>
@@ -3709,7 +3709,7 @@
         <v>432000</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="str">
         <f t="shared" si="1"/>
         <v>tirchm15</v>
@@ -3724,7 +3724,7 @@
         <v>432000</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="str">
         <f t="shared" si="1"/>
         <v>tirchm16</v>
@@ -3739,7 +3739,7 @@
         <v>432000</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="str">
         <f t="shared" si="1"/>
         <v>tirchm17</v>
@@ -3754,7 +3754,7 @@
         <v>432000</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="str">
         <f t="shared" si="1"/>
         <v>tirchm18</v>
@@ -3769,7 +3769,7 @@
         <v>432000</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="str">
         <f t="shared" si="1"/>
         <v>tirchm19</v>
@@ -3784,7 +3784,7 @@
         <v>432000</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="str">
         <f t="shared" si="1"/>
         <v>tirchm20</v>
@@ -3799,7 +3799,7 @@
         <v>432000</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="str">
         <f t="shared" si="1"/>
         <v>tirchm21</v>
@@ -3814,7 +3814,7 @@
         <v>432000</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="str">
         <f t="shared" si="1"/>
         <v>tirchm22</v>
@@ -3829,7 +3829,7 @@
         <v>432000</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="str">
         <f t="shared" si="1"/>
         <v>tirchm23</v>
@@ -3844,7 +3844,7 @@
         <v>432000</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="str">
         <f t="shared" si="1"/>
         <v>tirchm24</v>
@@ -3859,7 +3859,7 @@
         <v>432000</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="str">
         <f t="shared" si="1"/>
         <v>tirchm25</v>
@@ -3874,7 +3874,7 @@
         <v>432000</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="str">
         <f t="shared" si="1"/>
         <v>tirchm26</v>
@@ -3889,7 +3889,7 @@
         <v>432000</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="str">
         <f t="shared" si="1"/>
         <v>tirchm27</v>
@@ -3904,7 +3904,7 @@
         <v>432000</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="str">
         <f t="shared" si="1"/>
         <v>tirchm28</v>
@@ -3919,7 +3919,7 @@
         <v>432000</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="str">
         <f t="shared" si="1"/>
         <v>tirchm29</v>
@@ -3934,7 +3934,7 @@
         <v>432000</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="str">
         <f t="shared" si="1"/>
         <v>tirchm30</v>
@@ -3949,7 +3949,7 @@
         <v>432000</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="str">
         <f t="shared" si="1"/>
         <v>tirchm31</v>
@@ -3964,7 +3964,7 @@
         <v>432000</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="str">
         <f t="shared" si="1"/>
         <v>tirchm32</v>
@@ -3979,7 +3979,7 @@
         <v>432000</v>
       </c>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="str">
         <f t="shared" si="1"/>
         <v>tirchm33</v>
@@ -3994,7 +3994,7 @@
         <v>432000</v>
       </c>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="str">
         <f t="shared" si="1"/>
         <v>tirstl01</v>
@@ -4009,7 +4009,7 @@
         <v>604800</v>
       </c>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="str">
         <f t="shared" si="1"/>
         <v>tirstl02</v>
@@ -4024,7 +4024,7 @@
         <v>604800</v>
       </c>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="str">
         <f t="shared" si="1"/>
         <v>tirstl03</v>
@@ -4039,7 +4039,7 @@
         <v>604800</v>
       </c>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="str">
         <f t="shared" ref="A132:A195" si="2">"t"&amp;B132</f>
         <v>tirstl04</v>
@@ -4054,7 +4054,7 @@
         <v>604800</v>
       </c>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="str">
         <f t="shared" si="2"/>
         <v>tirstl05</v>
@@ -4069,7 +4069,7 @@
         <v>604800</v>
       </c>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="str">
         <f t="shared" si="2"/>
         <v>tirqsa01</v>
@@ -4084,7 +4084,7 @@
         <v>86400</v>
       </c>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="str">
         <f t="shared" si="2"/>
         <v>tirqsa03</v>
@@ -4099,7 +4099,7 @@
         <v>86400</v>
       </c>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="str">
         <f t="shared" si="2"/>
         <v>tirqsa05</v>
@@ -4114,7 +4114,7 @@
         <v>43200</v>
       </c>
     </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="str">
         <f t="shared" si="2"/>
         <v>tirqsa08</v>
@@ -4129,7 +4129,7 @@
         <v>172800</v>
       </c>
     </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="str">
         <f t="shared" si="2"/>
         <v>tirqsa07</v>
@@ -4144,7 +4144,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="str">
         <f t="shared" si="2"/>
         <v>tiwqsa01</v>
@@ -4159,7 +4159,7 @@
         <v>18000</v>
       </c>
     </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="str">
         <f t="shared" si="2"/>
         <v>tiwqsa02</v>
@@ -4174,7 +4174,7 @@
         <v>18000</v>
       </c>
     </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="str">
         <f t="shared" si="2"/>
         <v>tiwqsa03</v>
@@ -4189,7 +4189,7 @@
         <v>18000</v>
       </c>
     </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="str">
         <f t="shared" si="2"/>
         <v>tiwqsa04</v>
@@ -4204,7 +4204,7 @@
         <v>18000</v>
       </c>
     </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="str">
         <f t="shared" si="2"/>
         <v>tirqsa09</v>
@@ -4219,7 +4219,7 @@
         <v>172800</v>
       </c>
     </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="str">
         <f t="shared" si="2"/>
         <v>tirqsa10</v>
@@ -4234,7 +4234,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="str">
         <f t="shared" si="2"/>
         <v>tipqsa10</v>
@@ -4249,7 +4249,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="str">
         <f t="shared" si="2"/>
         <v>tirchm34</v>
@@ -4264,7 +4264,7 @@
         <v>7200</v>
       </c>
     </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="str">
         <f t="shared" si="2"/>
         <v>tirchm35</v>
@@ -4279,7 +4279,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="str">
         <f t="shared" si="2"/>
         <v>tirchm36</v>
@@ -4294,7 +4294,7 @@
         <v>21600</v>
       </c>
     </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="str">
         <f t="shared" si="2"/>
         <v>tirchm37</v>
@@ -4309,7 +4309,7 @@
         <v>43200</v>
       </c>
     </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="str">
         <f t="shared" si="2"/>
         <v>tirchm38</v>
@@ -4324,7 +4324,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="str">
         <f t="shared" si="2"/>
         <v>tirchm39</v>
@@ -4339,7 +4339,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="str">
         <f t="shared" si="2"/>
         <v>tirchm40</v>
@@ -4354,7 +4354,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="str">
         <f t="shared" si="2"/>
         <v>tirchm41</v>
@@ -4369,7 +4369,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="str">
         <f t="shared" si="2"/>
         <v>tirchm42</v>
@@ -4384,7 +4384,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="str">
         <f t="shared" si="2"/>
         <v>tirchm43</v>
@@ -4399,7 +4399,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="str">
         <f t="shared" si="2"/>
         <v>tirchm44</v>
@@ -4414,7 +4414,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="str">
         <f t="shared" si="2"/>
         <v>tirchm45</v>
@@ -4429,7 +4429,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="str">
         <f t="shared" si="2"/>
         <v>tipexp04</v>
@@ -4444,7 +4444,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="str">
         <f t="shared" si="2"/>
         <v>tipexp05</v>
@@ -4459,7 +4459,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="str">
         <f t="shared" si="2"/>
         <v>tipqsa24</v>
@@ -4474,7 +4474,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="str">
         <f t="shared" si="2"/>
         <v>tirval01</v>
@@ -4489,7 +4489,7 @@
         <v>604800</v>
       </c>
     </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="str">
         <f t="shared" si="2"/>
         <v>tiaqsa04</v>
@@ -4504,7 +4504,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="str">
         <f t="shared" si="2"/>
         <v>tiaqsa05</v>
@@ -4519,7 +4519,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="str">
         <f t="shared" si="2"/>
         <v>tiaqsa06</v>
@@ -4534,7 +4534,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="str">
         <f t="shared" si="2"/>
         <v>tiaqsa07</v>
@@ -4549,7 +4549,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="str">
         <f t="shared" si="2"/>
         <v>tiiqsa04</v>
@@ -4564,7 +4564,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="str">
         <f t="shared" si="2"/>
         <v>tiiqsa05</v>
@@ -4579,7 +4579,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="str">
         <f t="shared" si="2"/>
         <v>tirchm46</v>
@@ -4594,7 +4594,7 @@
         <v>432000</v>
       </c>
     </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="str">
         <f t="shared" si="2"/>
         <v>tirchm47</v>
@@ -4609,7 +4609,7 @@
         <v>432000</v>
       </c>
     </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="str">
         <f t="shared" si="2"/>
         <v>tirchm48</v>
@@ -4624,7 +4624,7 @@
         <v>432000</v>
       </c>
     </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="str">
         <f t="shared" si="2"/>
         <v>tirchm49</v>
@@ -4639,7 +4639,7 @@
         <v>432000</v>
       </c>
     </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="str">
         <f t="shared" si="2"/>
         <v>tirchm50</v>
@@ -4654,7 +4654,7 @@
         <v>432000</v>
       </c>
     </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="str">
         <f t="shared" si="2"/>
         <v>tirchm51</v>
@@ -4669,7 +4669,7 @@
         <v>432000</v>
       </c>
     </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="str">
         <f t="shared" si="2"/>
         <v>tirchm52</v>
@@ -4684,7 +4684,7 @@
         <v>432000</v>
       </c>
     </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="str">
         <f t="shared" si="2"/>
         <v>tirchm53</v>
@@ -4699,7 +4699,7 @@
         <v>432000</v>
       </c>
     </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="str">
         <f t="shared" si="2"/>
         <v>tirchm54</v>
@@ -4714,7 +4714,7 @@
         <v>432000</v>
       </c>
     </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="str">
         <f t="shared" si="2"/>
         <v>tirchm55</v>
@@ -4729,7 +4729,7 @@
         <v>432000</v>
       </c>
     </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="str">
         <f t="shared" si="2"/>
         <v>tirchm56</v>
@@ -4744,7 +4744,7 @@
         <v>432000</v>
       </c>
     </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="str">
         <f t="shared" si="2"/>
         <v>tirchm57</v>
@@ -4759,7 +4759,7 @@
         <v>432000</v>
       </c>
     </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="str">
         <f t="shared" si="2"/>
         <v>tihemy01</v>
@@ -4774,7 +4774,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="str">
         <f t="shared" si="2"/>
         <v>tihemy02</v>
@@ -4789,7 +4789,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="str">
         <f t="shared" si="2"/>
         <v>tihemy03</v>
@@ -4804,7 +4804,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="str">
         <f t="shared" si="2"/>
         <v>tihemy04</v>
@@ -4819,7 +4819,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="str">
         <f t="shared" si="2"/>
         <v>tihemy05</v>
@@ -4834,7 +4834,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="str">
         <f t="shared" si="2"/>
         <v>tihemy06</v>
@@ -4849,7 +4849,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="str">
         <f t="shared" si="2"/>
         <v>tihemy07</v>
@@ -4864,7 +4864,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="str">
         <f t="shared" si="2"/>
         <v>tihemy08</v>
@@ -4879,7 +4879,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="str">
         <f t="shared" si="2"/>
         <v>tihemy09</v>
@@ -4894,7 +4894,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="str">
         <f t="shared" si="2"/>
         <v>tihemy10</v>
@@ -4909,7 +4909,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="str">
         <f t="shared" si="2"/>
         <v>tihemy11</v>
@@ -4924,7 +4924,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="str">
         <f t="shared" si="2"/>
         <v>tihemy12</v>
@@ -4939,7 +4939,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="str">
         <f t="shared" si="2"/>
         <v>tihemy13</v>
@@ -4954,7 +4954,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="193" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="str">
         <f t="shared" si="2"/>
         <v>tihemy14</v>
@@ -4969,7 +4969,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="194" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="str">
         <f t="shared" si="2"/>
         <v>tihemy15</v>
@@ -4984,7 +4984,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="195" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="str">
         <f t="shared" si="2"/>
         <v>tihemy22</v>
@@ -4999,7 +4999,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="196" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="str">
         <f t="shared" ref="A196:A259" si="3">"t"&amp;B196</f>
         <v>tihemy23</v>
@@ -5014,7 +5014,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="197" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="str">
         <f t="shared" si="3"/>
         <v>tihemy24</v>
@@ -5029,7 +5029,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="198" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="str">
         <f t="shared" si="3"/>
         <v>tihemy25</v>
@@ -5044,7 +5044,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="199" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="str">
         <f t="shared" si="3"/>
         <v>tihemy26</v>
@@ -5059,7 +5059,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="200" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="str">
         <f t="shared" si="3"/>
         <v>tihemy27</v>
@@ -5074,7 +5074,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="201" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="str">
         <f t="shared" si="3"/>
         <v>tihemy28</v>
@@ -5089,7 +5089,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="202" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="str">
         <f t="shared" si="3"/>
         <v>tihemy29</v>
@@ -5104,7 +5104,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="203" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="str">
         <f t="shared" si="3"/>
         <v>tihemy30</v>
@@ -5119,7 +5119,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="204" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="str">
         <f t="shared" si="3"/>
         <v>tihemy31</v>
@@ -5134,7 +5134,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="205" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="str">
         <f t="shared" si="3"/>
         <v>tihemy32</v>
@@ -5149,7 +5149,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="206" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="str">
         <f t="shared" si="3"/>
         <v>tihemy33</v>
@@ -5164,7 +5164,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="207" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="str">
         <f t="shared" si="3"/>
         <v>tihemy34</v>
@@ -5179,7 +5179,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="208" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="str">
         <f t="shared" si="3"/>
         <v>tihemy35</v>
@@ -5194,7 +5194,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="209" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="str">
         <f t="shared" si="3"/>
         <v>tihemy36</v>
@@ -5209,7 +5209,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="210" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="str">
         <f t="shared" si="3"/>
         <v>tihemy43</v>
@@ -5224,7 +5224,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="211" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="str">
         <f t="shared" si="3"/>
         <v>tihemy44</v>
@@ -5239,7 +5239,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="212" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="str">
         <f t="shared" si="3"/>
         <v>tihemy45</v>
@@ -5254,7 +5254,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="213" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="str">
         <f t="shared" si="3"/>
         <v>tihemy46</v>
@@ -5269,7 +5269,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="214" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="str">
         <f t="shared" si="3"/>
         <v>tihemy47</v>
@@ -5284,7 +5284,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="215" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="str">
         <f t="shared" si="3"/>
         <v>tihemy48</v>
@@ -5299,7 +5299,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="216" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="str">
         <f t="shared" si="3"/>
         <v>tihemy49</v>
@@ -5314,7 +5314,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="217" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="str">
         <f t="shared" si="3"/>
         <v>tihemy50</v>
@@ -5329,7 +5329,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="218" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="str">
         <f t="shared" si="3"/>
         <v>tihemy51</v>
@@ -5344,7 +5344,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="219" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="str">
         <f t="shared" si="3"/>
         <v>tihemy52</v>
@@ -5359,7 +5359,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="220" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="str">
         <f t="shared" si="3"/>
         <v>tihemy53</v>
@@ -5374,7 +5374,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="221" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="str">
         <f t="shared" si="3"/>
         <v>tihemy54</v>
@@ -5389,7 +5389,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="222" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="str">
         <f t="shared" si="3"/>
         <v>tihemy55</v>
@@ -5404,7 +5404,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="223" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="str">
         <f t="shared" si="3"/>
         <v>tihemy56</v>
@@ -5419,7 +5419,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="224" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="str">
         <f t="shared" si="3"/>
         <v>tihemy57</v>
@@ -5434,7 +5434,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="225" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="str">
         <f t="shared" si="3"/>
         <v>tihemz01</v>
@@ -5449,7 +5449,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="226" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="str">
         <f t="shared" si="3"/>
         <v>tihemz02</v>
@@ -5464,7 +5464,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="227" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="str">
         <f t="shared" si="3"/>
         <v>tihemz03</v>
@@ -5479,7 +5479,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="228" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="str">
         <f t="shared" si="3"/>
         <v>tihemz04</v>
@@ -5494,7 +5494,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="229" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="str">
         <f t="shared" si="3"/>
         <v>tihemz05</v>
@@ -5509,7 +5509,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="230" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="str">
         <f t="shared" si="3"/>
         <v>tihemz06</v>
@@ -5524,7 +5524,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="231" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="str">
         <f t="shared" si="3"/>
         <v>tihemz07</v>
@@ -5539,7 +5539,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="232" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="str">
         <f t="shared" si="3"/>
         <v>tihemz08</v>
@@ -5554,7 +5554,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="233" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="str">
         <f t="shared" si="3"/>
         <v>tihemz09</v>
@@ -5569,7 +5569,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="234" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="str">
         <f t="shared" si="3"/>
         <v>tihemz10</v>
@@ -5584,7 +5584,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="235" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="str">
         <f t="shared" si="3"/>
         <v>tihemz11</v>
@@ -5599,7 +5599,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="236" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="str">
         <f t="shared" si="3"/>
         <v>tihemz12</v>
@@ -5614,7 +5614,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="237" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A237" s="1" t="str">
         <f t="shared" si="3"/>
         <v>tihemz13</v>
@@ -5629,7 +5629,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="238" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A238" s="1" t="str">
         <f t="shared" si="3"/>
         <v>tihemz14</v>
@@ -5644,7 +5644,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="239" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A239" s="1" t="str">
         <f t="shared" si="3"/>
         <v>tihemz15</v>
@@ -5659,7 +5659,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="240" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A240" s="1" t="str">
         <f t="shared" si="3"/>
         <v>tihemz22</v>
@@ -5674,7 +5674,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="241" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A241" s="1" t="str">
         <f t="shared" si="3"/>
         <v>tihemz23</v>
@@ -5689,7 +5689,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="242" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A242" s="1" t="str">
         <f t="shared" si="3"/>
         <v>tihemz24</v>
@@ -5704,7 +5704,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="243" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A243" s="1" t="str">
         <f t="shared" si="3"/>
         <v>tihemz25</v>
@@ -5719,7 +5719,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="244" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A244" s="1" t="str">
         <f t="shared" si="3"/>
         <v>tihemz26</v>
@@ -5734,7 +5734,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="245" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A245" s="1" t="str">
         <f t="shared" si="3"/>
         <v>tihemz27</v>
@@ -5749,7 +5749,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="246" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A246" s="1" t="str">
         <f t="shared" si="3"/>
         <v>tihemz28</v>
@@ -5764,7 +5764,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="247" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A247" s="1" t="str">
         <f t="shared" si="3"/>
         <v>tihemz29</v>
@@ -5779,7 +5779,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="248" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A248" s="1" t="str">
         <f t="shared" si="3"/>
         <v>tihemz30</v>
@@ -5794,7 +5794,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="249" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A249" s="1" t="str">
         <f t="shared" si="3"/>
         <v>tihemz31</v>
@@ -5809,7 +5809,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="250" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A250" s="1" t="str">
         <f t="shared" si="3"/>
         <v>tihemz32</v>
@@ -5824,7 +5824,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="251" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A251" s="1" t="str">
         <f t="shared" si="3"/>
         <v>tihemz33</v>
@@ -5839,7 +5839,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="252" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A252" s="1" t="str">
         <f t="shared" si="3"/>
         <v>tihemz34</v>
@@ -5854,7 +5854,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="253" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A253" s="1" t="str">
         <f t="shared" si="3"/>
         <v>tihemz35</v>
@@ -5869,7 +5869,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="254" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A254" s="1" t="str">
         <f t="shared" si="3"/>
         <v>tihemz36</v>
@@ -5884,7 +5884,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="255" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A255" s="1" t="str">
         <f t="shared" si="3"/>
         <v>tihemz43</v>
@@ -5899,7 +5899,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="256" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A256" s="1" t="str">
         <f t="shared" si="3"/>
         <v>tihemz44</v>
@@ -5914,7 +5914,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="257" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A257" s="1" t="str">
         <f t="shared" si="3"/>
         <v>tihemz45</v>
@@ -5929,7 +5929,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="258" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A258" s="1" t="str">
         <f t="shared" si="3"/>
         <v>tihemz46</v>
@@ -5944,7 +5944,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="259" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A259" s="1" t="str">
         <f t="shared" si="3"/>
         <v>tihemz47</v>
@@ -5959,7 +5959,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="260" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A260" s="1" t="str">
         <f t="shared" ref="A260:A323" si="4">"t"&amp;B260</f>
         <v>tihemz48</v>
@@ -5974,7 +5974,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="261" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A261" s="1" t="str">
         <f t="shared" si="4"/>
         <v>tihemz49</v>
@@ -5989,7 +5989,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="262" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A262" s="1" t="str">
         <f t="shared" si="4"/>
         <v>tihemz50</v>
@@ -6004,7 +6004,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="263" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A263" s="1" t="str">
         <f t="shared" si="4"/>
         <v>tihemz51</v>
@@ -6019,7 +6019,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="264" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A264" s="1" t="str">
         <f t="shared" si="4"/>
         <v>tihemz52</v>
@@ -6034,7 +6034,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="265" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A265" s="1" t="str">
         <f t="shared" si="4"/>
         <v>tihemz53</v>
@@ -6049,7 +6049,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="266" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A266" s="1" t="str">
         <f t="shared" si="4"/>
         <v>tihemz54</v>
@@ -6064,7 +6064,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="267" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A267" s="1" t="str">
         <f t="shared" si="4"/>
         <v>tihemz55</v>
@@ -6079,7 +6079,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="268" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A268" s="1" t="str">
         <f t="shared" si="4"/>
         <v>tihemz56</v>
@@ -6094,7 +6094,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="269" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A269" s="1" t="str">
         <f t="shared" si="4"/>
         <v>tihemz57</v>
@@ -6109,7 +6109,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="270" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A270" s="1" t="str">
         <f t="shared" si="4"/>
         <v>tihemy64</v>
@@ -6124,7 +6124,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="271" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A271" s="1" t="str">
         <f t="shared" si="4"/>
         <v>tihemy65</v>
@@ -6139,7 +6139,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="272" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A272" s="1" t="str">
         <f t="shared" si="4"/>
         <v>tihemy66</v>
@@ -6154,7 +6154,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="273" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A273" s="1" t="str">
         <f t="shared" si="4"/>
         <v>tihemy67</v>
@@ -6169,7 +6169,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="274" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A274" s="1" t="str">
         <f t="shared" si="4"/>
         <v>tihemy68</v>
@@ -6184,7 +6184,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="275" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A275" s="1" t="str">
         <f t="shared" si="4"/>
         <v>tihemy69</v>
@@ -6199,7 +6199,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="276" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A276" s="1" t="str">
         <f t="shared" si="4"/>
         <v>tihemy70</v>
@@ -6214,7 +6214,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="277" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A277" s="1" t="str">
         <f t="shared" si="4"/>
         <v>tihemy71</v>
@@ -6229,7 +6229,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="278" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A278" s="1" t="str">
         <f t="shared" si="4"/>
         <v>tihemy72</v>
@@ -6244,7 +6244,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="279" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A279" s="1" t="str">
         <f t="shared" si="4"/>
         <v>tihemz64</v>
@@ -6259,7 +6259,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="280" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A280" s="1" t="str">
         <f t="shared" si="4"/>
         <v>tihemz65</v>
@@ -6274,7 +6274,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="281" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A281" s="1" t="str">
         <f t="shared" si="4"/>
         <v>tihemz66</v>
@@ -6289,7 +6289,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="282" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A282" s="1" t="str">
         <f t="shared" si="4"/>
         <v>tihemz67</v>
@@ -6304,7 +6304,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="283" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A283" s="1" t="str">
         <f t="shared" si="4"/>
         <v>tihemz68</v>
@@ -6319,7 +6319,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="284" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A284" s="1" t="str">
         <f t="shared" si="4"/>
         <v>tihemz69</v>
@@ -6334,7 +6334,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="285" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A285" s="1" t="str">
         <f t="shared" si="4"/>
         <v>tihemz70</v>
@@ -6349,7 +6349,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="286" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A286" s="1" t="str">
         <f t="shared" si="4"/>
         <v>tihemz71</v>
@@ -6364,7 +6364,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="287" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A287" s="1" t="str">
         <f t="shared" si="4"/>
         <v>tihemz72</v>
@@ -6379,7 +6379,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="288" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A288" s="1" t="str">
         <f t="shared" si="4"/>
         <v>tihemy73</v>
@@ -6394,7 +6394,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="289" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A289" s="1" t="str">
         <f t="shared" si="4"/>
         <v>tihemy74</v>
@@ -6409,7 +6409,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="290" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A290" s="1" t="str">
         <f t="shared" si="4"/>
         <v>tihemy75</v>
@@ -6424,7 +6424,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="291" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A291" s="1" t="str">
         <f t="shared" si="4"/>
         <v>tihemy76</v>
@@ -6439,7 +6439,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="292" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A292" s="1" t="str">
         <f t="shared" si="4"/>
         <v>tihemy77</v>
@@ -6454,7 +6454,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="293" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A293" s="1" t="str">
         <f t="shared" si="4"/>
         <v>tihemy78</v>
@@ -6469,7 +6469,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="294" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A294" s="1" t="str">
         <f t="shared" si="4"/>
         <v>tihemy79</v>
@@ -6484,7 +6484,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="295" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A295" s="1" t="str">
         <f t="shared" si="4"/>
         <v>tihemy80</v>
@@ -6499,7 +6499,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="296" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A296" s="1" t="str">
         <f t="shared" si="4"/>
         <v>tihemy81</v>
@@ -6514,7 +6514,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="297" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A297" s="1" t="str">
         <f t="shared" si="4"/>
         <v>tihemz73</v>
@@ -6529,7 +6529,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="298" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A298" s="1" t="str">
         <f t="shared" si="4"/>
         <v>tihemz74</v>
@@ -6544,7 +6544,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="299" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A299" s="1" t="str">
         <f t="shared" si="4"/>
         <v>tihemz75</v>
@@ -6559,7 +6559,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="300" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A300" s="1" t="str">
         <f t="shared" si="4"/>
         <v>tihemz76</v>
@@ -6574,7 +6574,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="301" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A301" s="1" t="str">
         <f t="shared" si="4"/>
         <v>tihemz77</v>
@@ -6589,7 +6589,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="302" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A302" s="1" t="str">
         <f t="shared" si="4"/>
         <v>tihemz78</v>
@@ -6604,7 +6604,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="303" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A303" s="1" t="str">
         <f t="shared" si="4"/>
         <v>tihemz79</v>
@@ -6619,7 +6619,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="304" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A304" s="1" t="str">
         <f t="shared" si="4"/>
         <v>tihemz80</v>
@@ -6634,7 +6634,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="305" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A305" s="1" t="str">
         <f t="shared" si="4"/>
         <v>tihemz81</v>
@@ -6649,7 +6649,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="306" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A306" s="1" t="str">
         <f t="shared" si="4"/>
         <v>tirmap04</v>
@@ -6664,7 +6664,7 @@
         <v>604800</v>
       </c>
     </row>
-    <row r="307" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A307" s="1" t="str">
         <f t="shared" si="4"/>
         <v>tirmap05</v>
@@ -6679,7 +6679,7 @@
         <v>604800</v>
       </c>
     </row>
-    <row r="308" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A308" s="1" t="str">
         <f t="shared" si="4"/>
         <v>tirmap06</v>
@@ -6694,7 +6694,7 @@
         <v>604800</v>
       </c>
     </row>
-    <row r="309" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A309" s="1" t="str">
         <f t="shared" si="4"/>
         <v>tirmap07</v>
@@ -6709,7 +6709,7 @@
         <v>604800</v>
       </c>
     </row>
-    <row r="310" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A310" s="1" t="str">
         <f t="shared" si="4"/>
         <v>tirmap08</v>
@@ -6724,7 +6724,7 @@
         <v>604800</v>
       </c>
     </row>
-    <row r="311" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A311" s="1" t="str">
         <f t="shared" si="4"/>
         <v>tirmap09</v>
@@ -6739,7 +6739,7 @@
         <v>604800</v>
       </c>
     </row>
-    <row r="312" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A312" s="1" t="str">
         <f t="shared" si="4"/>
         <v>tirmap10</v>
@@ -6754,7 +6754,7 @@
         <v>604800</v>
       </c>
     </row>
-    <row r="313" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A313" s="1" t="str">
         <f t="shared" si="4"/>
         <v>tirmap11</v>
@@ -6769,7 +6769,7 @@
         <v>604800</v>
       </c>
     </row>
-    <row r="314" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A314" s="1" t="str">
         <f t="shared" si="4"/>
         <v>tirmap12</v>
@@ -6784,7 +6784,7 @@
         <v>604800</v>
       </c>
     </row>
-    <row r="315" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A315" s="1" t="str">
         <f t="shared" si="4"/>
         <v>tirmap13</v>
@@ -6799,7 +6799,7 @@
         <v>604800</v>
       </c>
     </row>
-    <row r="316" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A316" s="1" t="str">
         <f t="shared" si="4"/>
         <v>tirmap14</v>
@@ -6814,7 +6814,7 @@
         <v>604800</v>
       </c>
     </row>
-    <row r="317" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A317" s="1" t="str">
         <f t="shared" si="4"/>
         <v>tiicsa03</v>
@@ -6829,7 +6829,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="318" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A318" s="1" t="str">
         <f t="shared" si="4"/>
         <v>tiicsa03</v>
@@ -6844,7 +6844,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="319" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A319" s="1" t="str">
         <f t="shared" si="4"/>
         <v>tiicsa04</v>
@@ -6859,7 +6859,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="320" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A320" s="1" t="str">
         <f t="shared" si="4"/>
         <v>tiacsa03</v>
@@ -6874,7 +6874,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="321" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A321" s="1" t="str">
         <f t="shared" si="4"/>
         <v>tiacsa03</v>
@@ -6889,7 +6889,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="322" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A322" s="1" t="str">
         <f t="shared" si="4"/>
         <v>tiacsa04</v>
@@ -6904,7 +6904,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="323" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A323" s="1" t="str">
         <f t="shared" si="4"/>
         <v>tiwmlu55</v>
@@ -6919,7 +6919,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="324" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A324" s="1" t="str">
         <f t="shared" ref="A324:A387" si="5">"t"&amp;B324</f>
         <v>tircme55</v>
@@ -6934,7 +6934,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="325" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A325" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tiwrtn05</v>
@@ -6949,7 +6949,7 @@
         <v>604800</v>
       </c>
     </row>
-    <row r="326" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A326" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tiwrtn06</v>
@@ -6964,7 +6964,7 @@
         <v>604800</v>
       </c>
     </row>
-    <row r="327" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A327" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tiwrtn07</v>
@@ -6979,7 +6979,7 @@
         <v>604800</v>
       </c>
     </row>
-    <row r="328" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A328" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tiwrtn08</v>
@@ -6994,7 +6994,7 @@
         <v>604800</v>
       </c>
     </row>
-    <row r="329" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A329" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tiwrtn09</v>
@@ -7009,7 +7009,7 @@
         <v>604800</v>
       </c>
     </row>
-    <row r="330" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A330" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tiwrtn10</v>
@@ -7024,7 +7024,7 @@
         <v>604800</v>
       </c>
     </row>
-    <row r="331" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A331" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tiwrtn11</v>
@@ -7039,7 +7039,7 @@
         <v>604800</v>
       </c>
     </row>
-    <row r="332" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A332" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tiwrtn12</v>
@@ -7054,7 +7054,7 @@
         <v>604800</v>
       </c>
     </row>
-    <row r="333" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A333" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tiwrtn13</v>
@@ -7069,7 +7069,7 @@
         <v>604800</v>
       </c>
     </row>
-    <row r="334" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A334" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tiwrtn14</v>
@@ -7084,7 +7084,7 @@
         <v>604800</v>
       </c>
     </row>
-    <row r="335" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A335" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tiwrtn15</v>
@@ -7099,7 +7099,7 @@
         <v>604800</v>
       </c>
     </row>
-    <row r="336" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A336" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tiwrtn16</v>
@@ -7114,7 +7114,7 @@
         <v>604800</v>
       </c>
     </row>
-    <row r="337" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A337" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tiwrtn17</v>
@@ -7129,7 +7129,7 @@
         <v>604800</v>
       </c>
     </row>
-    <row r="338" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A338" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tiwrtn18</v>
@@ -7144,7 +7144,7 @@
         <v>604800</v>
       </c>
     </row>
-    <row r="339" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A339" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tiwrtn19</v>
@@ -7159,7 +7159,7 @@
         <v>604800</v>
       </c>
     </row>
-    <row r="340" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A340" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tiwrtn20</v>
@@ -7174,7 +7174,7 @@
         <v>604800</v>
       </c>
     </row>
-    <row r="341" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A341" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tiwrtn21</v>
@@ -7189,7 +7189,7 @@
         <v>604800</v>
       </c>
     </row>
-    <row r="342" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A342" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tiwrtn22</v>
@@ -7204,7 +7204,7 @@
         <v>604800</v>
       </c>
     </row>
-    <row r="343" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A343" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tiwrtn23</v>
@@ -7219,7 +7219,7 @@
         <v>604800</v>
       </c>
     </row>
-    <row r="344" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A344" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tiwrtn24</v>
@@ -7234,7 +7234,7 @@
         <v>604800</v>
       </c>
     </row>
-    <row r="345" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A345" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tiwrtn25</v>
@@ -7249,7 +7249,7 @@
         <v>604800</v>
       </c>
     </row>
-    <row r="346" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A346" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tiwrtn26</v>
@@ -7264,7 +7264,7 @@
         <v>604800</v>
       </c>
     </row>
-    <row r="347" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A347" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tiwrtn27</v>
@@ -7279,7 +7279,7 @@
         <v>604800</v>
       </c>
     </row>
-    <row r="348" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A348" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tiwrtn28</v>
@@ -7294,7 +7294,7 @@
         <v>604800</v>
       </c>
     </row>
-    <row r="349" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A349" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tiwrtn29</v>
@@ -7309,7 +7309,7 @@
         <v>604800</v>
       </c>
     </row>
-    <row r="350" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A350" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tirrtn01</v>
@@ -7324,7 +7324,7 @@
         <v>604800</v>
       </c>
     </row>
-    <row r="351" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A351" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tircha01</v>
@@ -7339,7 +7339,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="352" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A352" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tircha02</v>
@@ -7354,7 +7354,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="353" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A353" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tircha03</v>
@@ -7369,7 +7369,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="354" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A354" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tircha04</v>
@@ -7384,7 +7384,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="355" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A355" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tircha05</v>
@@ -7399,7 +7399,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="356" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A356" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tircha06</v>
@@ -7414,7 +7414,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="357" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A357" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tircha07</v>
@@ -7429,7 +7429,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="358" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A358" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tircha08</v>
@@ -7444,7 +7444,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="359" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A359" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tircha09</v>
@@ -7459,7 +7459,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="360" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A360" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tircha10</v>
@@ -7474,7 +7474,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="361" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A361" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tircha11</v>
@@ -7489,7 +7489,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="362" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A362" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tircha12</v>
@@ -7504,7 +7504,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="363" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A363" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tircha13</v>
@@ -7519,7 +7519,7 @@
         <v>1209600</v>
       </c>
     </row>
-    <row r="364" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A364" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tircha14</v>
@@ -7534,7 +7534,7 @@
         <v>1209600</v>
       </c>
     </row>
-    <row r="365" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A365" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tircha15</v>
@@ -7549,7 +7549,7 @@
         <v>1209600</v>
       </c>
     </row>
-    <row r="366" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A366" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tircha16</v>
@@ -7564,7 +7564,7 @@
         <v>1209600</v>
       </c>
     </row>
-    <row r="367" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A367" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tircha17</v>
@@ -7579,7 +7579,7 @@
         <v>1209600</v>
       </c>
     </row>
-    <row r="368" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A368" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tircha18</v>
@@ -7594,7 +7594,7 @@
         <v>1209600</v>
       </c>
     </row>
-    <row r="369" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A369" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tircha19</v>
@@ -7609,7 +7609,7 @@
         <v>1209600</v>
       </c>
     </row>
-    <row r="370" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A370" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tircha20</v>
@@ -7624,7 +7624,7 @@
         <v>1209600</v>
       </c>
     </row>
-    <row r="371" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A371" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tircha21</v>
@@ -7639,7 +7639,7 @@
         <v>1209600</v>
       </c>
     </row>
-    <row r="372" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A372" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tircha22</v>
@@ -7654,7 +7654,7 @@
         <v>1209600</v>
       </c>
     </row>
-    <row r="373" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A373" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tircha23</v>
@@ -7669,7 +7669,7 @@
         <v>1209600</v>
       </c>
     </row>
-    <row r="374" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A374" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tircha24</v>
@@ -7684,7 +7684,7 @@
         <v>1209600</v>
       </c>
     </row>
-    <row r="375" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A375" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tircha25</v>
@@ -7699,7 +7699,7 @@
         <v>1209600</v>
       </c>
     </row>
-    <row r="376" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A376" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tircha26</v>
@@ -7714,7 +7714,7 @@
         <v>1209600</v>
       </c>
     </row>
-    <row r="377" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A377" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tircha27</v>
@@ -7729,7 +7729,7 @@
         <v>1209600</v>
       </c>
     </row>
-    <row r="378" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A378" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tircha28</v>
@@ -7744,7 +7744,7 @@
         <v>1209600</v>
       </c>
     </row>
-    <row r="379" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A379" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tircha29</v>
@@ -7759,7 +7759,7 @@
         <v>1209600</v>
       </c>
     </row>
-    <row r="380" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A380" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tircha30</v>
@@ -7774,7 +7774,7 @@
         <v>1209600</v>
       </c>
     </row>
-    <row r="381" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A381" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tircha31</v>
@@ -7789,7 +7789,7 @@
         <v>1209600</v>
       </c>
     </row>
-    <row r="382" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A382" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tircha32</v>
@@ -7804,7 +7804,7 @@
         <v>1209600</v>
       </c>
     </row>
-    <row r="383" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A383" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tircha33</v>
@@ -7819,7 +7819,7 @@
         <v>1209600</v>
       </c>
     </row>
-    <row r="384" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A384" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tircha34</v>
@@ -7834,7 +7834,7 @@
         <v>1209600</v>
       </c>
     </row>
-    <row r="385" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A385" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tircha35</v>
@@ -7849,7 +7849,7 @@
         <v>1209600</v>
       </c>
     </row>
-    <row r="386" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A386" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tircha36</v>
@@ -7864,7 +7864,7 @@
         <v>1209600</v>
       </c>
     </row>
-    <row r="387" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A387" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tircha37</v>
@@ -7879,7 +7879,7 @@
         <v>1209600</v>
       </c>
     </row>
-    <row r="388" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A388" s="1" t="str">
         <f t="shared" ref="A388:A451" si="6">"t"&amp;B388</f>
         <v>tircha38</v>
@@ -7894,7 +7894,7 @@
         <v>1209600</v>
       </c>
     </row>
-    <row r="389" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A389" s="1" t="str">
         <f t="shared" si="6"/>
         <v>tircha39</v>
@@ -7909,7 +7909,7 @@
         <v>1209600</v>
       </c>
     </row>
-    <row r="390" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A390" s="1" t="str">
         <f t="shared" si="6"/>
         <v>tircha40</v>
@@ -7924,7 +7924,7 @@
         <v>1209600</v>
       </c>
     </row>
-    <row r="391" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A391" s="1" t="str">
         <f t="shared" si="6"/>
         <v>tircha41</v>
@@ -7939,7 +7939,7 @@
         <v>1209600</v>
       </c>
     </row>
-    <row r="392" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A392" s="1" t="str">
         <f t="shared" si="6"/>
         <v>tircha42</v>
@@ -7954,7 +7954,7 @@
         <v>1209600</v>
       </c>
     </row>
-    <row r="393" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A393" s="1" t="str">
         <f t="shared" si="6"/>
         <v>tircha43</v>
@@ -7969,7 +7969,7 @@
         <v>1209600</v>
       </c>
     </row>
-    <row r="394" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A394" s="1" t="str">
         <f t="shared" si="6"/>
         <v>tircha44</v>
@@ -7984,7 +7984,7 @@
         <v>1209600</v>
       </c>
     </row>
-    <row r="395" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A395" s="1" t="str">
         <f t="shared" si="6"/>
         <v>tircha45</v>
@@ -7999,7 +7999,7 @@
         <v>1209600</v>
       </c>
     </row>
-    <row r="396" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A396" s="1" t="str">
         <f t="shared" si="6"/>
         <v>tircha46</v>
@@ -8014,7 +8014,7 @@
         <v>1209600</v>
       </c>
     </row>
-    <row r="397" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A397" s="1" t="str">
         <f t="shared" si="6"/>
         <v>tircja01</v>
@@ -8029,7 +8029,7 @@
         <v>518400</v>
       </c>
     </row>
-    <row r="398" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A398" s="1" t="str">
         <f t="shared" si="6"/>
         <v>tircja02</v>
@@ -8044,7 +8044,7 @@
         <v>518400</v>
       </c>
     </row>
-    <row r="399" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A399" s="1" t="str">
         <f t="shared" si="6"/>
         <v>tircja03</v>
@@ -8059,7 +8059,7 @@
         <v>72000</v>
       </c>
     </row>
-    <row r="400" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A400" s="1" t="str">
         <f t="shared" si="6"/>
         <v>tircja04</v>
@@ -8074,7 +8074,7 @@
         <v>72000</v>
       </c>
     </row>
-    <row r="401" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A401" s="1" t="str">
         <f t="shared" si="6"/>
         <v>tircja05</v>
@@ -8089,7 +8089,7 @@
         <v>518400</v>
       </c>
     </row>
-    <row r="402" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A402" s="1" t="str">
         <f t="shared" si="6"/>
         <v>tircja06</v>
@@ -8104,7 +8104,7 @@
         <v>518400</v>
       </c>
     </row>
-    <row r="403" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A403" s="1" t="str">
         <f t="shared" si="6"/>
         <v>tircja07</v>
@@ -8119,7 +8119,7 @@
         <v>72000</v>
       </c>
     </row>
-    <row r="404" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A404" s="1" t="str">
         <f t="shared" si="6"/>
         <v>tircja08</v>
@@ -8134,7 +8134,7 @@
         <v>72000</v>
       </c>
     </row>
-    <row r="405" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A405" s="1" t="str">
         <f t="shared" si="6"/>
         <v>tirpre20</v>
@@ -8149,7 +8149,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="406" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A406" s="1" t="str">
         <f t="shared" si="6"/>
         <v>tikexp02</v>
@@ -8164,7 +8164,7 @@
         <v>259200</v>
       </c>
     </row>
-    <row r="407" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A407" s="1" t="str">
         <f t="shared" si="6"/>
         <v>tircja09</v>
@@ -8176,10 +8176,10 @@
         <v>2</v>
       </c>
       <c r="D407" s="1">
-        <v>7200</v>
-      </c>
-    </row>
-    <row r="408" spans="1:4" x14ac:dyDescent="0.3">
+        <v>2592000</v>
+      </c>
+    </row>
+    <row r="408" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A408" s="1" t="str">
         <f t="shared" si="6"/>
         <v>tircja10</v>
@@ -8194,7 +8194,7 @@
         <v>21600</v>
       </c>
     </row>
-    <row r="409" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A409" s="1" t="str">
         <f t="shared" si="6"/>
         <v>tircja11</v>
@@ -8209,7 +8209,7 @@
         <v>86400</v>
       </c>
     </row>
-    <row r="410" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A410" s="1" t="str">
         <f t="shared" si="6"/>
         <v>tipcha01</v>
@@ -8224,7 +8224,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="411" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A411" s="1" t="str">
         <f t="shared" si="6"/>
         <v>tipcha02</v>
@@ -8239,7 +8239,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="412" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A412" s="1" t="str">
         <f t="shared" si="6"/>
         <v>tipcha03</v>
@@ -8254,7 +8254,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="413" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A413" s="1" t="str">
         <f t="shared" si="6"/>
         <v>tiprun01</v>
@@ -8269,7 +8269,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="414" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A414" s="1" t="str">
         <f t="shared" si="6"/>
         <v>tiprun03</v>
@@ -8284,7 +8284,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="415" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A415" s="1" t="str">
         <f t="shared" si="6"/>
         <v>tiprun04</v>
@@ -8299,7 +8299,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="416" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A416" s="1" t="str">
         <f t="shared" si="6"/>
         <v>tiprun05</v>
@@ -8314,7 +8314,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="417" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A417" s="1" t="str">
         <f t="shared" si="6"/>
         <v>tiprun07</v>
@@ -8329,7 +8329,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="418" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A418" s="1" t="str">
         <f t="shared" si="6"/>
         <v>tiprun08</v>
@@ -8344,7 +8344,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="419" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A419" s="1" t="str">
         <f t="shared" si="6"/>
         <v>tiprun09</v>
@@ -8359,7 +8359,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="420" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A420" s="1" t="str">
         <f t="shared" si="6"/>
         <v>tikbb015</v>
@@ -8374,7 +8374,7 @@
         <v>259200</v>
       </c>
     </row>
-    <row r="421" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A421" s="1" t="str">
         <f t="shared" si="6"/>
         <v>tikbb016</v>
@@ -8389,7 +8389,7 @@
         <v>259200</v>
       </c>
     </row>
-    <row r="422" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A422" s="1" t="str">
         <f t="shared" si="6"/>
         <v>tikcc015</v>
@@ -8404,7 +8404,7 @@
         <v>259200</v>
       </c>
     </row>
-    <row r="423" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A423" s="1" t="str">
         <f t="shared" si="6"/>
         <v>tikcc016</v>
@@ -8419,7 +8419,7 @@
         <v>259200</v>
       </c>
     </row>
-    <row r="424" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A424" s="1" t="str">
         <f t="shared" si="6"/>
         <v>tikaa015</v>
@@ -8434,7 +8434,7 @@
         <v>259200</v>
       </c>
     </row>
-    <row r="425" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A425" s="1" t="str">
         <f t="shared" si="6"/>
         <v>tikaa016</v>
@@ -8449,7 +8449,7 @@
         <v>259200</v>
       </c>
     </row>
-    <row r="426" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A426" s="1" t="str">
         <f t="shared" si="6"/>
         <v>tikbb017</v>
@@ -8464,7 +8464,7 @@
         <v>1296000</v>
       </c>
     </row>
-    <row r="427" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A427" s="1" t="str">
         <f t="shared" si="6"/>
         <v>tikbb018</v>
@@ -8479,7 +8479,7 @@
         <v>1296000</v>
       </c>
     </row>
-    <row r="428" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A428" s="1" t="str">
         <f t="shared" si="6"/>
         <v>tikcc017</v>
@@ -8494,7 +8494,7 @@
         <v>1296000</v>
       </c>
     </row>
-    <row r="429" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A429" s="1" t="str">
         <f t="shared" si="6"/>
         <v>tikcc018</v>
@@ -8509,7 +8509,7 @@
         <v>1296000</v>
       </c>
     </row>
-    <row r="430" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A430" s="1" t="str">
         <f t="shared" si="6"/>
         <v>tikaa017</v>
@@ -8524,7 +8524,7 @@
         <v>1296000</v>
       </c>
     </row>
-    <row r="431" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A431" s="1" t="str">
         <f t="shared" si="6"/>
         <v>tikaa018</v>
@@ -8539,7 +8539,7 @@
         <v>1296000</v>
       </c>
     </row>
-    <row r="432" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A432" s="1" t="str">
         <f t="shared" si="6"/>
         <v>tikqsa01</v>
@@ -8554,7 +8554,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="433" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A433" s="1" t="str">
         <f t="shared" si="6"/>
         <v>tikbb019</v>
@@ -8569,7 +8569,7 @@
         <v>432000</v>
       </c>
     </row>
-    <row r="434" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A434" s="1" t="str">
         <f t="shared" si="6"/>
         <v>tikbb020</v>
@@ -8584,7 +8584,7 @@
         <v>432000</v>
       </c>
     </row>
-    <row r="435" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A435" s="1" t="str">
         <f t="shared" si="6"/>
         <v>tikcc019</v>
@@ -8599,7 +8599,7 @@
         <v>432000</v>
       </c>
     </row>
-    <row r="436" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A436" s="1" t="str">
         <f t="shared" si="6"/>
         <v>tikcc020</v>
@@ -8614,7 +8614,7 @@
         <v>432000</v>
       </c>
     </row>
-    <row r="437" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A437" s="1" t="str">
         <f t="shared" si="6"/>
         <v>tikaa019</v>
@@ -8629,7 +8629,7 @@
         <v>432000</v>
       </c>
     </row>
-    <row r="438" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A438" s="1" t="str">
         <f t="shared" si="6"/>
         <v>tikaa020</v>
@@ -8644,7 +8644,7 @@
         <v>432000</v>
       </c>
     </row>
-    <row r="439" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A439" s="1" t="str">
         <f t="shared" si="6"/>
         <v>tirlif01</v>
@@ -8659,7 +8659,7 @@
         <v>172800</v>
       </c>
     </row>
-    <row r="440" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A440" s="1" t="str">
         <f t="shared" si="6"/>
         <v>tirlif02</v>
@@ -8674,7 +8674,7 @@
         <v>604800</v>
       </c>
     </row>
-    <row r="441" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A441" s="1" t="str">
         <f t="shared" si="6"/>
         <v>tirlif03</v>
@@ -8689,7 +8689,7 @@
         <v>1209600</v>
       </c>
     </row>
-    <row r="442" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A442" s="1" t="str">
         <f t="shared" si="6"/>
         <v>tirlif01</v>
@@ -8704,7 +8704,7 @@
         <v>172800</v>
       </c>
     </row>
-    <row r="443" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A443" s="1" t="str">
         <f t="shared" si="6"/>
         <v>tirlif02</v>
@@ -8719,7 +8719,7 @@
         <v>604800</v>
       </c>
     </row>
-    <row r="444" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A444" s="1" t="str">
         <f t="shared" si="6"/>
         <v>tirlif03</v>
@@ -8734,7 +8734,7 @@
         <v>1209600</v>
       </c>
     </row>
-    <row r="445" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A445" s="1" t="str">
         <f t="shared" si="6"/>
         <v>tirlif04</v>
@@ -8749,7 +8749,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="446" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A446" s="1" t="str">
         <f t="shared" si="6"/>
         <v>tikaa035</v>
@@ -8764,7 +8764,7 @@
         <v>259200</v>
       </c>
     </row>
-    <row r="447" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A447" s="1" t="str">
         <f t="shared" si="6"/>
         <v>tikaa036</v>
@@ -8779,7 +8779,7 @@
         <v>259200</v>
       </c>
     </row>
-    <row r="448" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A448" s="1" t="str">
         <f t="shared" si="6"/>
         <v>tikaa037</v>
@@ -8794,7 +8794,7 @@
         <v>432000</v>
       </c>
     </row>
-    <row r="449" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A449" s="1" t="str">
         <f t="shared" si="6"/>
         <v>tikaa038</v>
@@ -8809,7 +8809,7 @@
         <v>432000</v>
       </c>
     </row>
-    <row r="450" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A450" s="1" t="str">
         <f t="shared" si="6"/>
         <v>tikaa039</v>
@@ -8824,7 +8824,7 @@
         <v>1296000</v>
       </c>
     </row>
-    <row r="451" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A451" s="1" t="str">
         <f t="shared" si="6"/>
         <v>tikaa040</v>
@@ -8839,7 +8839,7 @@
         <v>1296000</v>
       </c>
     </row>
-    <row r="452" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A452" s="1" t="str">
         <f t="shared" ref="A452:A515" si="7">"t"&amp;B452</f>
         <v>tikbb035</v>
@@ -8854,7 +8854,7 @@
         <v>259200</v>
       </c>
     </row>
-    <row r="453" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A453" s="1" t="str">
         <f t="shared" si="7"/>
         <v>tikbb036</v>
@@ -8869,7 +8869,7 @@
         <v>259200</v>
       </c>
     </row>
-    <row r="454" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A454" s="1" t="str">
         <f t="shared" si="7"/>
         <v>tikbb037</v>
@@ -8884,7 +8884,7 @@
         <v>432000</v>
       </c>
     </row>
-    <row r="455" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A455" s="1" t="str">
         <f t="shared" si="7"/>
         <v>tikbb038</v>
@@ -8899,7 +8899,7 @@
         <v>432000</v>
       </c>
     </row>
-    <row r="456" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A456" s="1" t="str">
         <f t="shared" si="7"/>
         <v>tikbb039</v>
@@ -8914,7 +8914,7 @@
         <v>1296000</v>
       </c>
     </row>
-    <row r="457" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A457" s="1" t="str">
         <f t="shared" si="7"/>
         <v>tikbb040</v>
@@ -8929,7 +8929,7 @@
         <v>1296000</v>
       </c>
     </row>
-    <row r="458" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A458" s="1" t="str">
         <f t="shared" si="7"/>
         <v>tikcc035</v>
@@ -8944,7 +8944,7 @@
         <v>259200</v>
       </c>
     </row>
-    <row r="459" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A459" s="1" t="str">
         <f t="shared" si="7"/>
         <v>tikcc036</v>
@@ -8959,7 +8959,7 @@
         <v>259200</v>
       </c>
     </row>
-    <row r="460" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A460" s="1" t="str">
         <f t="shared" si="7"/>
         <v>tikcc037</v>
@@ -8974,7 +8974,7 @@
         <v>432000</v>
       </c>
     </row>
-    <row r="461" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A461" s="1" t="str">
         <f t="shared" si="7"/>
         <v>tikcc038</v>
@@ -8989,7 +8989,7 @@
         <v>432000</v>
       </c>
     </row>
-    <row r="462" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A462" s="1" t="str">
         <f t="shared" si="7"/>
         <v>tikcc039</v>
@@ -9004,7 +9004,7 @@
         <v>1296000</v>
       </c>
     </row>
-    <row r="463" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A463" s="1" t="str">
         <f t="shared" si="7"/>
         <v>tikcc040</v>
@@ -9019,7 +9019,7 @@
         <v>1296000</v>
       </c>
     </row>
-    <row r="464" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A464" s="1" t="str">
         <f t="shared" si="7"/>
         <v>tiprun02</v>
@@ -9034,7 +9034,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="465" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A465" s="1" t="str">
         <f t="shared" si="7"/>
         <v>tiyqst01</v>
@@ -9049,7 +9049,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="466" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A466" s="1" t="str">
         <f t="shared" si="7"/>
         <v>tihbwf65</v>
@@ -9064,7 +9064,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="467" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A467" s="1" t="str">
         <f t="shared" si="7"/>
         <v>tiubwf65</v>
@@ -9079,7 +9079,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="468" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A468" s="1" t="str">
         <f t="shared" si="7"/>
         <v>tilbwf65</v>
@@ -9094,7 +9094,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="469" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A469" s="1" t="str">
         <f t="shared" si="7"/>
         <v>tigbwf65</v>
@@ -9109,7 +9109,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="470" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A470" s="1" t="str">
         <f t="shared" si="7"/>
         <v>tisbwf65</v>
@@ -9124,7 +9124,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="471" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A471" s="1" t="str">
         <f t="shared" si="7"/>
         <v>tihbrf65</v>
@@ -9139,7 +9139,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="472" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A472" s="1" t="str">
         <f t="shared" si="7"/>
         <v>tiubrf65</v>
@@ -9154,7 +9154,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="473" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A473" s="1" t="str">
         <f t="shared" si="7"/>
         <v>tilbrf65</v>
@@ -9169,7 +9169,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="474" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A474" s="1" t="str">
         <f t="shared" si="7"/>
         <v>tigbrf65</v>
@@ -9184,7 +9184,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="475" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A475" s="1" t="str">
         <f t="shared" si="7"/>
         <v>tisbrf65</v>
@@ -9199,7 +9199,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="476" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A476" s="1" t="str">
         <f t="shared" si="7"/>
         <v>tihbff65</v>
@@ -9214,7 +9214,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="477" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A477" s="1" t="str">
         <f t="shared" si="7"/>
         <v>tiubff65</v>
@@ -9229,7 +9229,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="478" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A478" s="1" t="str">
         <f t="shared" si="7"/>
         <v>tilbff65</v>
@@ -9244,7 +9244,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="479" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A479" s="1" t="str">
         <f t="shared" si="7"/>
         <v>tigbff65</v>
@@ -9259,7 +9259,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="480" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A480" s="1" t="str">
         <f t="shared" si="7"/>
         <v>tisbff65</v>
@@ -9274,7 +9274,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="481" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A481" s="1" t="str">
         <f t="shared" si="7"/>
         <v>tihcwf65</v>
@@ -9289,7 +9289,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="482" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A482" s="1" t="str">
         <f t="shared" si="7"/>
         <v>tiucwf65</v>
@@ -9304,7 +9304,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="483" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A483" s="1" t="str">
         <f t="shared" si="7"/>
         <v>tilcwf65</v>
@@ -9319,7 +9319,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="484" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A484" s="1" t="str">
         <f t="shared" si="7"/>
         <v>tigcwf65</v>
@@ -9334,7 +9334,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="485" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A485" s="1" t="str">
         <f t="shared" si="7"/>
         <v>tiscwf65</v>
@@ -9349,7 +9349,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="486" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A486" s="1" t="str">
         <f t="shared" si="7"/>
         <v>tihcrf65</v>
@@ -9364,7 +9364,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="487" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A487" s="1" t="str">
         <f t="shared" si="7"/>
         <v>tiucrf65</v>
@@ -9379,7 +9379,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="488" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A488" s="1" t="str">
         <f t="shared" si="7"/>
         <v>tilcrf65</v>
@@ -9394,7 +9394,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="489" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A489" s="1" t="str">
         <f t="shared" si="7"/>
         <v>tigcrf65</v>
@@ -9409,7 +9409,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="490" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A490" s="1" t="str">
         <f t="shared" si="7"/>
         <v>tiscrf65</v>
@@ -9424,7 +9424,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="491" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A491" s="1" t="str">
         <f t="shared" si="7"/>
         <v>tihcff65</v>
@@ -9439,7 +9439,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="492" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A492" s="1" t="str">
         <f t="shared" si="7"/>
         <v>tiucff65</v>
@@ -9454,7 +9454,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="493" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A493" s="1" t="str">
         <f t="shared" si="7"/>
         <v>tilcff65</v>
@@ -9469,7 +9469,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="494" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A494" s="1" t="str">
         <f t="shared" si="7"/>
         <v>tigcff65</v>
@@ -9484,7 +9484,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="495" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A495" s="1" t="str">
         <f t="shared" si="7"/>
         <v>tiscff65</v>
@@ -9499,7 +9499,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="496" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A496" s="1" t="str">
         <f t="shared" si="7"/>
         <v>tihawf65</v>
@@ -9514,7 +9514,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="497" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A497" s="1" t="str">
         <f t="shared" si="7"/>
         <v>tiuawf65</v>
@@ -9529,7 +9529,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="498" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A498" s="1" t="str">
         <f t="shared" si="7"/>
         <v>tilawf65</v>
@@ -9544,7 +9544,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="499" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A499" s="1" t="str">
         <f t="shared" si="7"/>
         <v>tigawf65</v>
@@ -9559,7 +9559,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="500" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A500" s="1" t="str">
         <f t="shared" si="7"/>
         <v>tisawf65</v>
@@ -9574,7 +9574,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="501" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A501" s="1" t="str">
         <f t="shared" si="7"/>
         <v>tiharf65</v>
@@ -9589,7 +9589,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="502" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A502" s="1" t="str">
         <f t="shared" si="7"/>
         <v>tiuarf65</v>
@@ -9604,7 +9604,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="503" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A503" s="1" t="str">
         <f t="shared" si="7"/>
         <v>tilarf65</v>
@@ -9619,7 +9619,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="504" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A504" s="1" t="str">
         <f t="shared" si="7"/>
         <v>tigarf65</v>
@@ -9634,7 +9634,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="505" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A505" s="1" t="str">
         <f t="shared" si="7"/>
         <v>tisarf65</v>
@@ -9649,7 +9649,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="506" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A506" s="1" t="str">
         <f t="shared" si="7"/>
         <v>tihaff65</v>
@@ -9664,7 +9664,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="507" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A507" s="1" t="str">
         <f t="shared" si="7"/>
         <v>tiuaff65</v>
@@ -9679,7 +9679,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="508" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A508" s="1" t="str">
         <f t="shared" si="7"/>
         <v>tilaff65</v>
@@ -9694,7 +9694,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="509" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A509" s="1" t="str">
         <f t="shared" si="7"/>
         <v>tigaff65</v>
@@ -9709,7 +9709,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="510" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A510" s="1" t="str">
         <f t="shared" si="7"/>
         <v>tisaff65</v>
@@ -9724,7 +9724,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="511" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A511" s="1" t="str">
         <f t="shared" si="7"/>
         <v>tiwstf24</v>
@@ -9739,7 +9739,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="512" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A512" s="1" t="str">
         <f t="shared" si="7"/>
         <v>tiwspf24</v>
@@ -9754,7 +9754,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="513" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A513" s="1" t="str">
         <f t="shared" si="7"/>
         <v>tiwbof24</v>
@@ -9769,7 +9769,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="514" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A514" s="1" t="str">
         <f t="shared" si="7"/>
         <v>tiwfif24</v>
@@ -9784,7 +9784,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="515" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A515" s="1" t="str">
         <f t="shared" si="7"/>
         <v>tiwluf24</v>
@@ -9799,7 +9799,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="516" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A516" s="1" t="str">
         <f t="shared" ref="A516:A561" si="8">"t"&amp;B516</f>
         <v>tiwgef24</v>
@@ -9814,7 +9814,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="517" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A517" s="1" t="str">
         <f t="shared" si="8"/>
         <v>tidaaf65</v>
@@ -9829,7 +9829,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="518" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A518" s="1" t="str">
         <f t="shared" si="8"/>
         <v>tidbcf65</v>
@@ -9844,7 +9844,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="519" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A519" s="1" t="str">
         <f t="shared" si="8"/>
         <v>tiibbx25</v>
@@ -9859,7 +9859,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="520" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A520" s="1" t="str">
         <f t="shared" si="8"/>
         <v>tiibbx50</v>
@@ -9874,7 +9874,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="521" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A521" s="1" t="str">
         <f t="shared" si="8"/>
         <v>tiiaax25</v>
@@ -9889,7 +9889,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="522" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A522" s="1" t="str">
         <f t="shared" si="8"/>
         <v>tiiaax50</v>
@@ -9904,7 +9904,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="523" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A523" s="1" t="str">
         <f t="shared" si="8"/>
         <v>tiiccx10</v>
@@ -9919,7 +9919,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="524" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A524" s="1" t="str">
         <f t="shared" si="8"/>
         <v>tiaaax25</v>
@@ -9934,7 +9934,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="525" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A525" s="1" t="str">
         <f t="shared" si="8"/>
         <v>tiaaax50</v>
@@ -9949,7 +9949,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="526" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A526" s="1" t="str">
         <f t="shared" si="8"/>
         <v>tiabbx15</v>
@@ -9964,7 +9964,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="527" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A527" s="1" t="str">
         <f t="shared" si="8"/>
         <v>tiaccx50</v>
@@ -9979,7 +9979,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="528" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A528" s="1" t="str">
         <f t="shared" si="8"/>
         <v>tiaccx80</v>
@@ -9994,7 +9994,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="529" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A529" s="1" t="str">
         <f t="shared" si="8"/>
         <v>tirtal14</v>
@@ -10009,7 +10009,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="530" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A530" s="1" t="str">
         <f t="shared" si="8"/>
         <v>tiprun06</v>
@@ -10024,7 +10024,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="531" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A531" s="1" t="str">
         <f t="shared" si="8"/>
         <v>tiwevn02</v>
@@ -10039,7 +10039,7 @@
         <v>604800</v>
       </c>
     </row>
-    <row r="532" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A532" s="1" t="str">
         <f t="shared" si="8"/>
         <v>tircme56</v>
@@ -10054,7 +10054,7 @@
         <v>43200</v>
       </c>
     </row>
-    <row r="533" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A533" s="1" t="str">
         <f t="shared" si="8"/>
         <v>tikbb014</v>
@@ -10069,7 +10069,7 @@
         <v>604800</v>
       </c>
     </row>
-    <row r="534" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A534" s="1" t="str">
         <f t="shared" si="8"/>
         <v>tikcc014</v>
@@ -10084,7 +10084,7 @@
         <v>604800</v>
       </c>
     </row>
-    <row r="535" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A535" s="1" t="str">
         <f t="shared" si="8"/>
         <v>tikaa014</v>
@@ -10099,7 +10099,7 @@
         <v>604800</v>
       </c>
     </row>
-    <row r="536" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A536" s="1" t="str">
         <f t="shared" si="8"/>
         <v>tigbwf66</v>
@@ -10114,7 +10114,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="537" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A537" s="1" t="str">
         <f t="shared" si="8"/>
         <v>tigbrf66</v>
@@ -10129,7 +10129,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="538" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A538" s="1" t="str">
         <f t="shared" si="8"/>
         <v>tigbff66</v>
@@ -10144,7 +10144,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="539" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A539" s="1" t="str">
         <f t="shared" si="8"/>
         <v>tigcwf66</v>
@@ -10159,7 +10159,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="540" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A540" s="1" t="str">
         <f t="shared" si="8"/>
         <v>tigcrf66</v>
@@ -10174,7 +10174,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="541" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A541" s="1" t="str">
         <f t="shared" si="8"/>
         <v>tigcff66</v>
@@ -10189,7 +10189,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="542" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A542" s="1" t="str">
         <f t="shared" si="8"/>
         <v>tigawf66</v>
@@ -10204,7 +10204,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="543" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A543" s="1" t="str">
         <f t="shared" si="8"/>
         <v>tigarf66</v>
@@ -10219,7 +10219,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="544" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A544" s="1" t="str">
         <f t="shared" si="8"/>
         <v>tigaff66</v>
@@ -10234,7 +10234,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="545" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A545" s="1" t="str">
         <f t="shared" si="8"/>
         <v>tisbwf66</v>
@@ -10249,7 +10249,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="546" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A546" s="1" t="str">
         <f t="shared" si="8"/>
         <v>tisbrf66</v>
@@ -10264,7 +10264,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="547" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A547" s="1" t="str">
         <f t="shared" si="8"/>
         <v>tisbff66</v>
@@ -10279,7 +10279,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="548" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A548" s="1" t="str">
         <f t="shared" si="8"/>
         <v>tiscwf66</v>
@@ -10294,7 +10294,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="549" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A549" s="1" t="str">
         <f t="shared" si="8"/>
         <v>tiscrf66</v>
@@ -10309,7 +10309,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="550" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A550" s="1" t="str">
         <f t="shared" si="8"/>
         <v>tiscff66</v>
@@ -10324,7 +10324,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="551" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A551" s="1" t="str">
         <f t="shared" si="8"/>
         <v>tisawf66</v>
@@ -10339,7 +10339,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="552" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A552" s="1" t="str">
         <f t="shared" si="8"/>
         <v>tisarf66</v>
@@ -10354,7 +10354,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="553" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A553" s="1" t="str">
         <f t="shared" si="8"/>
         <v>tisaff66</v>
@@ -10369,7 +10369,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="554" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A554" s="1" t="str">
         <f t="shared" si="8"/>
         <v>tirpre01</v>
@@ -10384,7 +10384,7 @@
         <v>86400</v>
       </c>
     </row>
-    <row r="555" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A555" s="1" t="str">
         <f t="shared" si="8"/>
         <v>tsklu022</v>
@@ -10399,7 +10399,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="556" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A556" s="1" t="str">
         <f t="shared" si="8"/>
         <v>tsklu025</v>
@@ -10414,7 +10414,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="557" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A557" s="1" t="str">
         <f t="shared" si="8"/>
         <v>tibbnn05</v>
@@ -10429,7 +10429,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="558" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A558" s="1" t="str">
         <f t="shared" si="8"/>
         <v>tipexp02</v>
@@ -10444,7 +10444,7 @@
         <v>3600</v>
       </c>
     </row>
-    <row r="559" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A559" s="1" t="str">
         <f t="shared" si="8"/>
         <v>tirpre02</v>
@@ -10459,7 +10459,7 @@
         <v>259200</v>
       </c>
     </row>
-    <row r="560" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A560" s="1" t="str">
         <f t="shared" si="8"/>
         <v>tiwevn23</v>
@@ -10474,7 +10474,7 @@
         <v>1209600</v>
       </c>
     </row>
-    <row r="561" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A561" s="1" t="str">
         <f t="shared" si="8"/>
         <v>tirpre03</v>

--- a/gu_in/ItemTimer.edf/TimerItem.xlsx
+++ b/gu_in/ItemTimer.edf/TimerItem.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA5F3A2E-0B58-4DE7-BBA9-1EE6A28A0FD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC324745-9CEB-45BD-BB1E-AF9753CDA049}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TimerItem" sheetId="1" r:id="rId1"/>
@@ -1757,9 +1757,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1778,9 +1779,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1818,9 +1819,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1853,9 +1854,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1888,9 +1906,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2064,7 +2099,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E561"/>
+  <dimension ref="A1:F561"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="9.42578125" bestFit="1" customWidth="1"/>
@@ -7114,7 +7149,7 @@
         <v>604800</v>
       </c>
     </row>
-    <row r="337" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A337" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tiwrtn17</v>
@@ -7129,7 +7164,7 @@
         <v>604800</v>
       </c>
     </row>
-    <row r="338" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A338" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tiwrtn18</v>
@@ -7144,7 +7179,7 @@
         <v>604800</v>
       </c>
     </row>
-    <row r="339" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A339" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tiwrtn19</v>
@@ -7159,7 +7194,7 @@
         <v>604800</v>
       </c>
     </row>
-    <row r="340" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A340" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tiwrtn20</v>
@@ -7174,7 +7209,7 @@
         <v>604800</v>
       </c>
     </row>
-    <row r="341" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A341" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tiwrtn21</v>
@@ -7189,7 +7224,7 @@
         <v>604800</v>
       </c>
     </row>
-    <row r="342" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A342" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tiwrtn22</v>
@@ -7204,7 +7239,7 @@
         <v>604800</v>
       </c>
     </row>
-    <row r="343" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A343" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tiwrtn23</v>
@@ -7219,7 +7254,7 @@
         <v>604800</v>
       </c>
     </row>
-    <row r="344" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A344" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tiwrtn24</v>
@@ -7234,7 +7269,7 @@
         <v>604800</v>
       </c>
     </row>
-    <row r="345" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A345" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tiwrtn25</v>
@@ -7249,7 +7284,7 @@
         <v>604800</v>
       </c>
     </row>
-    <row r="346" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A346" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tiwrtn26</v>
@@ -7264,7 +7299,7 @@
         <v>604800</v>
       </c>
     </row>
-    <row r="347" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A347" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tiwrtn27</v>
@@ -7279,7 +7314,7 @@
         <v>604800</v>
       </c>
     </row>
-    <row r="348" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A348" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tiwrtn28</v>
@@ -7294,7 +7329,7 @@
         <v>604800</v>
       </c>
     </row>
-    <row r="349" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A349" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tiwrtn29</v>
@@ -7309,7 +7344,7 @@
         <v>604800</v>
       </c>
     </row>
-    <row r="350" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A350" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tirrtn01</v>
@@ -7324,7 +7359,7 @@
         <v>604800</v>
       </c>
     </row>
-    <row r="351" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A351" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tircha01</v>
@@ -7336,10 +7371,11 @@
         <v>2</v>
       </c>
       <c r="D351" s="1">
-        <v>2592000</v>
-      </c>
-    </row>
-    <row r="352" spans="1:4" x14ac:dyDescent="0.25">
+        <v>604800</v>
+      </c>
+      <c r="F351" s="2"/>
+    </row>
+    <row r="352" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A352" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tircha02</v>
@@ -7351,10 +7387,11 @@
         <v>2</v>
       </c>
       <c r="D352" s="1">
-        <v>2592000</v>
-      </c>
-    </row>
-    <row r="353" spans="1:4" x14ac:dyDescent="0.25">
+        <v>604800</v>
+      </c>
+      <c r="F352" s="2"/>
+    </row>
+    <row r="353" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A353" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tircha03</v>
@@ -7366,10 +7403,11 @@
         <v>2</v>
       </c>
       <c r="D353" s="1">
-        <v>2592000</v>
-      </c>
-    </row>
-    <row r="354" spans="1:4" x14ac:dyDescent="0.25">
+        <v>604800</v>
+      </c>
+      <c r="F353" s="2"/>
+    </row>
+    <row r="354" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A354" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tircha04</v>
@@ -7381,10 +7419,11 @@
         <v>2</v>
       </c>
       <c r="D354" s="1">
-        <v>2592000</v>
-      </c>
-    </row>
-    <row r="355" spans="1:4" x14ac:dyDescent="0.25">
+        <v>604800</v>
+      </c>
+      <c r="F354" s="2"/>
+    </row>
+    <row r="355" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A355" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tircha05</v>
@@ -7396,10 +7435,11 @@
         <v>2</v>
       </c>
       <c r="D355" s="1">
-        <v>2592000</v>
-      </c>
-    </row>
-    <row r="356" spans="1:4" x14ac:dyDescent="0.25">
+        <v>604800</v>
+      </c>
+      <c r="F355" s="2"/>
+    </row>
+    <row r="356" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A356" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tircha06</v>
@@ -7411,10 +7451,11 @@
         <v>2</v>
       </c>
       <c r="D356" s="1">
-        <v>2592000</v>
-      </c>
-    </row>
-    <row r="357" spans="1:4" x14ac:dyDescent="0.25">
+        <v>604800</v>
+      </c>
+      <c r="F356" s="2"/>
+    </row>
+    <row r="357" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A357" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tircha07</v>
@@ -7426,10 +7467,11 @@
         <v>2</v>
       </c>
       <c r="D357" s="1">
-        <v>2592000</v>
-      </c>
-    </row>
-    <row r="358" spans="1:4" x14ac:dyDescent="0.25">
+        <v>604800</v>
+      </c>
+      <c r="F357" s="2"/>
+    </row>
+    <row r="358" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A358" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tircha08</v>
@@ -7441,10 +7483,11 @@
         <v>2</v>
       </c>
       <c r="D358" s="1">
-        <v>2592000</v>
-      </c>
-    </row>
-    <row r="359" spans="1:4" x14ac:dyDescent="0.25">
+        <v>604800</v>
+      </c>
+      <c r="F358" s="2"/>
+    </row>
+    <row r="359" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A359" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tircha09</v>
@@ -7456,10 +7499,11 @@
         <v>2</v>
       </c>
       <c r="D359" s="1">
-        <v>2592000</v>
-      </c>
-    </row>
-    <row r="360" spans="1:4" x14ac:dyDescent="0.25">
+        <v>604800</v>
+      </c>
+      <c r="F359" s="2"/>
+    </row>
+    <row r="360" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A360" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tircha10</v>
@@ -7471,10 +7515,11 @@
         <v>2</v>
       </c>
       <c r="D360" s="1">
-        <v>2592000</v>
-      </c>
-    </row>
-    <row r="361" spans="1:4" x14ac:dyDescent="0.25">
+        <v>604800</v>
+      </c>
+      <c r="F360" s="2"/>
+    </row>
+    <row r="361" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A361" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tircha11</v>
@@ -7486,10 +7531,11 @@
         <v>2</v>
       </c>
       <c r="D361" s="1">
-        <v>2592000</v>
-      </c>
-    </row>
-    <row r="362" spans="1:4" x14ac:dyDescent="0.25">
+        <v>604800</v>
+      </c>
+      <c r="F361" s="2"/>
+    </row>
+    <row r="362" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A362" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tircha12</v>
@@ -7501,10 +7547,11 @@
         <v>2</v>
       </c>
       <c r="D362" s="1">
-        <v>2592000</v>
-      </c>
-    </row>
-    <row r="363" spans="1:4" x14ac:dyDescent="0.25">
+        <v>604800</v>
+      </c>
+      <c r="F362" s="2"/>
+    </row>
+    <row r="363" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A363" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tircha13</v>
@@ -7516,10 +7563,11 @@
         <v>2</v>
       </c>
       <c r="D363" s="1">
-        <v>1209600</v>
-      </c>
-    </row>
-    <row r="364" spans="1:4" x14ac:dyDescent="0.25">
+        <v>1296000</v>
+      </c>
+      <c r="F363" s="2"/>
+    </row>
+    <row r="364" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A364" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tircha14</v>
@@ -7531,10 +7579,11 @@
         <v>2</v>
       </c>
       <c r="D364" s="1">
-        <v>1209600</v>
-      </c>
-    </row>
-    <row r="365" spans="1:4" x14ac:dyDescent="0.25">
+        <v>1296000</v>
+      </c>
+      <c r="F364" s="2"/>
+    </row>
+    <row r="365" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A365" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tircha15</v>
@@ -7546,10 +7595,11 @@
         <v>2</v>
       </c>
       <c r="D365" s="1">
-        <v>1209600</v>
-      </c>
-    </row>
-    <row r="366" spans="1:4" x14ac:dyDescent="0.25">
+        <v>1296000</v>
+      </c>
+      <c r="F365" s="2"/>
+    </row>
+    <row r="366" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A366" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tircha16</v>
@@ -7561,10 +7611,11 @@
         <v>2</v>
       </c>
       <c r="D366" s="1">
-        <v>1209600</v>
-      </c>
-    </row>
-    <row r="367" spans="1:4" x14ac:dyDescent="0.25">
+        <v>1296000</v>
+      </c>
+      <c r="F366" s="2"/>
+    </row>
+    <row r="367" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A367" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tircha17</v>
@@ -7576,10 +7627,11 @@
         <v>2</v>
       </c>
       <c r="D367" s="1">
-        <v>1209600</v>
-      </c>
-    </row>
-    <row r="368" spans="1:4" x14ac:dyDescent="0.25">
+        <v>1296000</v>
+      </c>
+      <c r="F367" s="2"/>
+    </row>
+    <row r="368" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A368" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tircha18</v>
@@ -7591,10 +7643,11 @@
         <v>2</v>
       </c>
       <c r="D368" s="1">
-        <v>1209600</v>
-      </c>
-    </row>
-    <row r="369" spans="1:4" x14ac:dyDescent="0.25">
+        <v>1296000</v>
+      </c>
+      <c r="F368" s="2"/>
+    </row>
+    <row r="369" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A369" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tircha19</v>
@@ -7606,10 +7659,11 @@
         <v>2</v>
       </c>
       <c r="D369" s="1">
-        <v>1209600</v>
-      </c>
-    </row>
-    <row r="370" spans="1:4" x14ac:dyDescent="0.25">
+        <v>1296000</v>
+      </c>
+      <c r="F369" s="2"/>
+    </row>
+    <row r="370" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A370" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tircha20</v>
@@ -7621,10 +7675,11 @@
         <v>2</v>
       </c>
       <c r="D370" s="1">
-        <v>1209600</v>
-      </c>
-    </row>
-    <row r="371" spans="1:4" x14ac:dyDescent="0.25">
+        <v>1296000</v>
+      </c>
+      <c r="F370" s="2"/>
+    </row>
+    <row r="371" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A371" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tircha21</v>
@@ -7636,10 +7691,11 @@
         <v>2</v>
       </c>
       <c r="D371" s="1">
-        <v>1209600</v>
-      </c>
-    </row>
-    <row r="372" spans="1:4" x14ac:dyDescent="0.25">
+        <v>1296000</v>
+      </c>
+      <c r="F371" s="2"/>
+    </row>
+    <row r="372" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A372" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tircha22</v>
@@ -7651,10 +7707,11 @@
         <v>2</v>
       </c>
       <c r="D372" s="1">
-        <v>1209600</v>
-      </c>
-    </row>
-    <row r="373" spans="1:4" x14ac:dyDescent="0.25">
+        <v>1296000</v>
+      </c>
+      <c r="F372" s="2"/>
+    </row>
+    <row r="373" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A373" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tircha23</v>
@@ -7666,10 +7723,11 @@
         <v>2</v>
       </c>
       <c r="D373" s="1">
-        <v>1209600</v>
-      </c>
-    </row>
-    <row r="374" spans="1:4" x14ac:dyDescent="0.25">
+        <v>1296000</v>
+      </c>
+      <c r="F373" s="2"/>
+    </row>
+    <row r="374" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A374" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tircha24</v>
@@ -7681,10 +7739,11 @@
         <v>2</v>
       </c>
       <c r="D374" s="1">
-        <v>1209600</v>
-      </c>
-    </row>
-    <row r="375" spans="1:4" x14ac:dyDescent="0.25">
+        <v>1296000</v>
+      </c>
+      <c r="F374" s="2"/>
+    </row>
+    <row r="375" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A375" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tircha25</v>
@@ -7699,7 +7758,7 @@
         <v>1209600</v>
       </c>
     </row>
-    <row r="376" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A376" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tircha26</v>
@@ -7714,7 +7773,7 @@
         <v>1209600</v>
       </c>
     </row>
-    <row r="377" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A377" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tircha27</v>
@@ -7729,7 +7788,7 @@
         <v>1209600</v>
       </c>
     </row>
-    <row r="378" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A378" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tircha28</v>
@@ -7744,7 +7803,7 @@
         <v>1209600</v>
       </c>
     </row>
-    <row r="379" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A379" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tircha29</v>
@@ -7759,7 +7818,7 @@
         <v>1209600</v>
       </c>
     </row>
-    <row r="380" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A380" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tircha30</v>
@@ -7774,7 +7833,7 @@
         <v>1209600</v>
       </c>
     </row>
-    <row r="381" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A381" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tircha31</v>
@@ -7789,7 +7848,7 @@
         <v>1209600</v>
       </c>
     </row>
-    <row r="382" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A382" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tircha32</v>
@@ -7804,7 +7863,7 @@
         <v>1209600</v>
       </c>
     </row>
-    <row r="383" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A383" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tircha33</v>
@@ -7819,7 +7878,7 @@
         <v>1209600</v>
       </c>
     </row>
-    <row r="384" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A384" s="1" t="str">
         <f t="shared" si="5"/>
         <v>tircha34</v>

--- a/gu_in/ItemTimer.edf/TimerItem.xlsx
+++ b/gu_in/ItemTimer.edf/TimerItem.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC324745-9CEB-45BD-BB1E-AF9753CDA049}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C568986E-2B7B-400C-B483-31C041134131}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/gu_in/ItemTimer.edf/TimerItem.xlsx
+++ b/gu_in/ItemTimer.edf/TimerItem.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C568986E-2B7B-400C-B483-31C041134131}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4481996-DC07-4248-80A5-1430348954C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TimerItem" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="561">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="567" uniqueCount="560">
   <si>
     <t>string[64]</t>
   </si>
@@ -1616,9 +1616,6 @@
   </si>
   <si>
     <t>iprun06</t>
-  </si>
-  <si>
-    <t>iwevn02</t>
   </si>
   <si>
     <t>ircme56</t>
@@ -1779,9 +1776,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1819,9 +1816,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1854,26 +1851,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1906,26 +1886,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2099,7 +2062,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F561"/>
+  <dimension ref="A1:F560"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="9.42578125" bestFit="1" customWidth="1"/>
@@ -9860,7 +9823,7 @@
     </row>
     <row r="516" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A516" s="1" t="str">
-        <f t="shared" ref="A516:A561" si="8">"t"&amp;B516</f>
+        <f t="shared" ref="A516:A560" si="8">"t"&amp;B516</f>
         <v>tiwgef24</v>
       </c>
       <c r="B516" s="1" t="s">
@@ -10086,7 +10049,7 @@
     <row r="531" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A531" s="1" t="str">
         <f t="shared" si="8"/>
-        <v>tiwevn02</v>
+        <v>tircme56</v>
       </c>
       <c r="B531" s="1" t="s">
         <v>530</v>
@@ -10095,13 +10058,13 @@
         <v>2</v>
       </c>
       <c r="D531" s="1">
-        <v>604800</v>
+        <v>43200</v>
       </c>
     </row>
     <row r="532" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A532" s="1" t="str">
         <f t="shared" si="8"/>
-        <v>tircme56</v>
+        <v>tikbb014</v>
       </c>
       <c r="B532" s="1" t="s">
         <v>531</v>
@@ -10110,13 +10073,13 @@
         <v>2</v>
       </c>
       <c r="D532" s="1">
-        <v>43200</v>
+        <v>604800</v>
       </c>
     </row>
     <row r="533" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A533" s="1" t="str">
         <f t="shared" si="8"/>
-        <v>tikbb014</v>
+        <v>tikcc014</v>
       </c>
       <c r="B533" s="1" t="s">
         <v>532</v>
@@ -10131,7 +10094,7 @@
     <row r="534" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A534" s="1" t="str">
         <f t="shared" si="8"/>
-        <v>tikcc014</v>
+        <v>tikaa014</v>
       </c>
       <c r="B534" s="1" t="s">
         <v>533</v>
@@ -10146,7 +10109,7 @@
     <row r="535" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A535" s="1" t="str">
         <f t="shared" si="8"/>
-        <v>tikaa014</v>
+        <v>tigbwf66</v>
       </c>
       <c r="B535" s="1" t="s">
         <v>534</v>
@@ -10155,13 +10118,13 @@
         <v>2</v>
       </c>
       <c r="D535" s="1">
-        <v>604800</v>
+        <v>2592000</v>
       </c>
     </row>
     <row r="536" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A536" s="1" t="str">
         <f t="shared" si="8"/>
-        <v>tigbwf66</v>
+        <v>tigbrf66</v>
       </c>
       <c r="B536" s="1" t="s">
         <v>535</v>
@@ -10176,7 +10139,7 @@
     <row r="537" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A537" s="1" t="str">
         <f t="shared" si="8"/>
-        <v>tigbrf66</v>
+        <v>tigbff66</v>
       </c>
       <c r="B537" s="1" t="s">
         <v>536</v>
@@ -10191,7 +10154,7 @@
     <row r="538" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A538" s="1" t="str">
         <f t="shared" si="8"/>
-        <v>tigbff66</v>
+        <v>tigcwf66</v>
       </c>
       <c r="B538" s="1" t="s">
         <v>537</v>
@@ -10206,7 +10169,7 @@
     <row r="539" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A539" s="1" t="str">
         <f t="shared" si="8"/>
-        <v>tigcwf66</v>
+        <v>tigcrf66</v>
       </c>
       <c r="B539" s="1" t="s">
         <v>538</v>
@@ -10221,7 +10184,7 @@
     <row r="540" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A540" s="1" t="str">
         <f t="shared" si="8"/>
-        <v>tigcrf66</v>
+        <v>tigcff66</v>
       </c>
       <c r="B540" s="1" t="s">
         <v>539</v>
@@ -10236,7 +10199,7 @@
     <row r="541" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A541" s="1" t="str">
         <f t="shared" si="8"/>
-        <v>tigcff66</v>
+        <v>tigawf66</v>
       </c>
       <c r="B541" s="1" t="s">
         <v>540</v>
@@ -10251,7 +10214,7 @@
     <row r="542" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A542" s="1" t="str">
         <f t="shared" si="8"/>
-        <v>tigawf66</v>
+        <v>tigarf66</v>
       </c>
       <c r="B542" s="1" t="s">
         <v>541</v>
@@ -10266,7 +10229,7 @@
     <row r="543" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A543" s="1" t="str">
         <f t="shared" si="8"/>
-        <v>tigarf66</v>
+        <v>tigaff66</v>
       </c>
       <c r="B543" s="1" t="s">
         <v>542</v>
@@ -10281,7 +10244,7 @@
     <row r="544" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A544" s="1" t="str">
         <f t="shared" si="8"/>
-        <v>tigaff66</v>
+        <v>tisbwf66</v>
       </c>
       <c r="B544" s="1" t="s">
         <v>543</v>
@@ -10296,7 +10259,7 @@
     <row r="545" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A545" s="1" t="str">
         <f t="shared" si="8"/>
-        <v>tisbwf66</v>
+        <v>tisbrf66</v>
       </c>
       <c r="B545" s="1" t="s">
         <v>544</v>
@@ -10311,7 +10274,7 @@
     <row r="546" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A546" s="1" t="str">
         <f t="shared" si="8"/>
-        <v>tisbrf66</v>
+        <v>tisbff66</v>
       </c>
       <c r="B546" s="1" t="s">
         <v>545</v>
@@ -10326,7 +10289,7 @@
     <row r="547" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A547" s="1" t="str">
         <f t="shared" si="8"/>
-        <v>tisbff66</v>
+        <v>tiscwf66</v>
       </c>
       <c r="B547" s="1" t="s">
         <v>546</v>
@@ -10341,7 +10304,7 @@
     <row r="548" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A548" s="1" t="str">
         <f t="shared" si="8"/>
-        <v>tiscwf66</v>
+        <v>tiscrf66</v>
       </c>
       <c r="B548" s="1" t="s">
         <v>547</v>
@@ -10356,7 +10319,7 @@
     <row r="549" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A549" s="1" t="str">
         <f t="shared" si="8"/>
-        <v>tiscrf66</v>
+        <v>tiscff66</v>
       </c>
       <c r="B549" s="1" t="s">
         <v>548</v>
@@ -10371,7 +10334,7 @@
     <row r="550" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A550" s="1" t="str">
         <f t="shared" si="8"/>
-        <v>tiscff66</v>
+        <v>tisawf66</v>
       </c>
       <c r="B550" s="1" t="s">
         <v>549</v>
@@ -10386,7 +10349,7 @@
     <row r="551" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A551" s="1" t="str">
         <f t="shared" si="8"/>
-        <v>tisawf66</v>
+        <v>tisarf66</v>
       </c>
       <c r="B551" s="1" t="s">
         <v>550</v>
@@ -10401,7 +10364,7 @@
     <row r="552" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A552" s="1" t="str">
         <f t="shared" si="8"/>
-        <v>tisarf66</v>
+        <v>tisaff66</v>
       </c>
       <c r="B552" s="1" t="s">
         <v>551</v>
@@ -10416,7 +10379,7 @@
     <row r="553" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A553" s="1" t="str">
         <f t="shared" si="8"/>
-        <v>tisaff66</v>
+        <v>tirpre01</v>
       </c>
       <c r="B553" s="1" t="s">
         <v>552</v>
@@ -10425,13 +10388,13 @@
         <v>2</v>
       </c>
       <c r="D553" s="1">
-        <v>2592000</v>
+        <v>86400</v>
       </c>
     </row>
     <row r="554" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A554" s="1" t="str">
         <f t="shared" si="8"/>
-        <v>tirpre01</v>
+        <v>tsklu022</v>
       </c>
       <c r="B554" s="1" t="s">
         <v>553</v>
@@ -10440,13 +10403,13 @@
         <v>2</v>
       </c>
       <c r="D554" s="1">
-        <v>86400</v>
+        <v>14400</v>
       </c>
     </row>
     <row r="555" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A555" s="1" t="str">
         <f t="shared" si="8"/>
-        <v>tsklu022</v>
+        <v>tsklu025</v>
       </c>
       <c r="B555" s="1" t="s">
         <v>554</v>
@@ -10461,7 +10424,7 @@
     <row r="556" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A556" s="1" t="str">
         <f t="shared" si="8"/>
-        <v>tsklu025</v>
+        <v>tibbnn05</v>
       </c>
       <c r="B556" s="1" t="s">
         <v>555</v>
@@ -10476,7 +10439,7 @@
     <row r="557" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A557" s="1" t="str">
         <f t="shared" si="8"/>
-        <v>tibbnn05</v>
+        <v>tipexp02</v>
       </c>
       <c r="B557" s="1" t="s">
         <v>556</v>
@@ -10485,13 +10448,13 @@
         <v>2</v>
       </c>
       <c r="D557" s="1">
-        <v>14400</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="558" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A558" s="1" t="str">
         <f t="shared" si="8"/>
-        <v>tipexp02</v>
+        <v>tirpre02</v>
       </c>
       <c r="B558" s="1" t="s">
         <v>557</v>
@@ -10500,13 +10463,13 @@
         <v>2</v>
       </c>
       <c r="D558" s="1">
-        <v>3600</v>
+        <v>259200</v>
       </c>
     </row>
     <row r="559" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A559" s="1" t="str">
         <f t="shared" si="8"/>
-        <v>tirpre02</v>
+        <v>tiwevn23</v>
       </c>
       <c r="B559" s="1" t="s">
         <v>558</v>
@@ -10515,13 +10478,13 @@
         <v>2</v>
       </c>
       <c r="D559" s="1">
-        <v>259200</v>
+        <v>1209600</v>
       </c>
     </row>
     <row r="560" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A560" s="1" t="str">
         <f t="shared" si="8"/>
-        <v>tiwevn23</v>
+        <v>tirpre03</v>
       </c>
       <c r="B560" s="1" t="s">
         <v>559</v>
@@ -10530,21 +10493,6 @@
         <v>2</v>
       </c>
       <c r="D560" s="1">
-        <v>1209600</v>
-      </c>
-    </row>
-    <row r="561" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A561" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>tirpre03</v>
-      </c>
-      <c r="B561" s="1" t="s">
-        <v>560</v>
-      </c>
-      <c r="C561" s="1">
-        <v>2</v>
-      </c>
-      <c r="D561" s="1">
         <v>14400</v>
       </c>
     </row>

--- a/gu_in/ItemTimer.edf/TimerItem.xlsx
+++ b/gu_in/ItemTimer.edf/TimerItem.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4481996-DC07-4248-80A5-1430348954C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B80CB4AC-5E2E-4C61-B34C-A740B65C24B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TimerItem" sheetId="1" r:id="rId1"/>
@@ -1776,9 +1776,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1816,9 +1816,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1851,9 +1851,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1886,9 +1903,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -4472,7 +4506,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="str">
         <f t="shared" si="2"/>
         <v>tirval01</v>
@@ -4487,7 +4521,7 @@
         <v>604800</v>
       </c>
     </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="str">
         <f t="shared" si="2"/>
         <v>tiaqsa04</v>
@@ -4502,7 +4536,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="str">
         <f t="shared" si="2"/>
         <v>tiaqsa05</v>
@@ -4517,7 +4551,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="str">
         <f t="shared" si="2"/>
         <v>tiaqsa06</v>
@@ -4532,7 +4566,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="str">
         <f t="shared" si="2"/>
         <v>tiaqsa07</v>
@@ -4547,7 +4581,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="str">
         <f t="shared" si="2"/>
         <v>tiiqsa04</v>
@@ -4562,7 +4596,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="str">
         <f t="shared" si="2"/>
         <v>tiiqsa05</v>
@@ -4577,7 +4611,7 @@
         <v>2592000</v>
       </c>
     </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="str">
         <f t="shared" si="2"/>
         <v>tirchm46</v>
@@ -4589,10 +4623,11 @@
         <v>2</v>
       </c>
       <c r="D168" s="1">
-        <v>432000</v>
-      </c>
-    </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
+        <v>259200</v>
+      </c>
+      <c r="F168" s="2"/>
+    </row>
+    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="str">
         <f t="shared" si="2"/>
         <v>tirchm47</v>
@@ -4604,10 +4639,11 @@
         <v>2</v>
       </c>
       <c r="D169" s="1">
-        <v>432000</v>
-      </c>
-    </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
+        <v>259200</v>
+      </c>
+      <c r="F169" s="2"/>
+    </row>
+    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="str">
         <f t="shared" si="2"/>
         <v>tirchm48</v>
@@ -4619,10 +4655,11 @@
         <v>2</v>
       </c>
       <c r="D170" s="1">
-        <v>432000</v>
-      </c>
-    </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
+        <v>259200</v>
+      </c>
+      <c r="F170" s="2"/>
+    </row>
+    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="str">
         <f t="shared" si="2"/>
         <v>tirchm49</v>
@@ -4634,10 +4671,11 @@
         <v>2</v>
       </c>
       <c r="D171" s="1">
-        <v>432000</v>
-      </c>
-    </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
+        <v>259200</v>
+      </c>
+      <c r="F171" s="2"/>
+    </row>
+    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="str">
         <f t="shared" si="2"/>
         <v>tirchm50</v>
@@ -4649,10 +4687,11 @@
         <v>2</v>
       </c>
       <c r="D172" s="1">
-        <v>432000</v>
-      </c>
-    </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
+        <v>259200</v>
+      </c>
+      <c r="F172" s="2"/>
+    </row>
+    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="str">
         <f t="shared" si="2"/>
         <v>tirchm51</v>
@@ -4664,10 +4703,11 @@
         <v>2</v>
       </c>
       <c r="D173" s="1">
-        <v>432000</v>
-      </c>
-    </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
+        <v>259200</v>
+      </c>
+      <c r="F173" s="2"/>
+    </row>
+    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="str">
         <f t="shared" si="2"/>
         <v>tirchm52</v>
@@ -4679,10 +4719,11 @@
         <v>2</v>
       </c>
       <c r="D174" s="1">
-        <v>432000</v>
-      </c>
-    </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
+        <v>259200</v>
+      </c>
+      <c r="F174" s="2"/>
+    </row>
+    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="str">
         <f t="shared" si="2"/>
         <v>tirchm53</v>
@@ -4694,10 +4735,11 @@
         <v>2</v>
       </c>
       <c r="D175" s="1">
-        <v>432000</v>
-      </c>
-    </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
+        <v>259200</v>
+      </c>
+      <c r="F175" s="2"/>
+    </row>
+    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="str">
         <f t="shared" si="2"/>
         <v>tirchm54</v>
@@ -4709,10 +4751,11 @@
         <v>2</v>
       </c>
       <c r="D176" s="1">
-        <v>432000</v>
-      </c>
-    </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
+        <v>259200</v>
+      </c>
+      <c r="F176" s="2"/>
+    </row>
+    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="str">
         <f t="shared" si="2"/>
         <v>tirchm55</v>
@@ -4724,10 +4767,11 @@
         <v>2</v>
       </c>
       <c r="D177" s="1">
-        <v>432000</v>
-      </c>
-    </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
+        <v>259200</v>
+      </c>
+      <c r="F177" s="2"/>
+    </row>
+    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="str">
         <f t="shared" si="2"/>
         <v>tirchm56</v>
@@ -4739,10 +4783,11 @@
         <v>2</v>
       </c>
       <c r="D178" s="1">
-        <v>432000</v>
-      </c>
-    </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
+        <v>259200</v>
+      </c>
+      <c r="F178" s="2"/>
+    </row>
+    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="str">
         <f t="shared" si="2"/>
         <v>tirchm57</v>
@@ -4754,10 +4799,11 @@
         <v>2</v>
       </c>
       <c r="D179" s="1">
-        <v>432000</v>
-      </c>
-    </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
+        <v>259200</v>
+      </c>
+      <c r="F179" s="2"/>
+    </row>
+    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="str">
         <f t="shared" si="2"/>
         <v>tihemy01</v>
@@ -4772,7 +4818,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="str">
         <f t="shared" si="2"/>
         <v>tihemy02</v>
@@ -4787,7 +4833,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="str">
         <f t="shared" si="2"/>
         <v>tihemy03</v>
@@ -4802,7 +4848,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="str">
         <f t="shared" si="2"/>
         <v>tihemy04</v>
@@ -4817,7 +4863,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="str">
         <f t="shared" si="2"/>
         <v>tihemy05</v>
@@ -4832,7 +4878,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="str">
         <f t="shared" si="2"/>
         <v>tihemy06</v>
@@ -4847,7 +4893,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="str">
         <f t="shared" si="2"/>
         <v>tihemy07</v>
@@ -4862,7 +4908,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="str">
         <f t="shared" si="2"/>
         <v>tihemy08</v>
@@ -4877,7 +4923,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="str">
         <f t="shared" si="2"/>
         <v>tihemy09</v>
@@ -4892,7 +4938,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="str">
         <f t="shared" si="2"/>
         <v>tihemy10</v>
@@ -4907,7 +4953,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="str">
         <f t="shared" si="2"/>
         <v>tihemy11</v>
@@ -4922,7 +4968,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="str">
         <f t="shared" si="2"/>
         <v>tihemy12</v>
@@ -4937,7 +4983,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="str">
         <f t="shared" si="2"/>
         <v>tihemy13</v>

--- a/gu_in/ItemTimer.edf/TimerItem.xlsx
+++ b/gu_in/ItemTimer.edf/TimerItem.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B80CB4AC-5E2E-4C61-B34C-A740B65C24B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA75358C-FFB6-4E3B-A451-9DEF8D55BDD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7572,7 +7572,7 @@
         <v>2</v>
       </c>
       <c r="D363" s="1">
-        <v>1296000</v>
+        <v>604800</v>
       </c>
       <c r="F363" s="2"/>
     </row>
@@ -7588,7 +7588,7 @@
         <v>2</v>
       </c>
       <c r="D364" s="1">
-        <v>1296000</v>
+        <v>604800</v>
       </c>
       <c r="F364" s="2"/>
     </row>
@@ -7604,7 +7604,7 @@
         <v>2</v>
       </c>
       <c r="D365" s="1">
-        <v>1296000</v>
+        <v>604800</v>
       </c>
       <c r="F365" s="2"/>
     </row>
@@ -7620,7 +7620,7 @@
         <v>2</v>
       </c>
       <c r="D366" s="1">
-        <v>1296000</v>
+        <v>604800</v>
       </c>
       <c r="F366" s="2"/>
     </row>
@@ -7636,7 +7636,7 @@
         <v>2</v>
       </c>
       <c r="D367" s="1">
-        <v>1296000</v>
+        <v>604800</v>
       </c>
       <c r="F367" s="2"/>
     </row>
@@ -7652,7 +7652,7 @@
         <v>2</v>
       </c>
       <c r="D368" s="1">
-        <v>1296000</v>
+        <v>604800</v>
       </c>
       <c r="F368" s="2"/>
     </row>
@@ -7668,7 +7668,7 @@
         <v>2</v>
       </c>
       <c r="D369" s="1">
-        <v>1296000</v>
+        <v>604800</v>
       </c>
       <c r="F369" s="2"/>
     </row>
@@ -7684,7 +7684,7 @@
         <v>2</v>
       </c>
       <c r="D370" s="1">
-        <v>1296000</v>
+        <v>604800</v>
       </c>
       <c r="F370" s="2"/>
     </row>
@@ -7700,7 +7700,7 @@
         <v>2</v>
       </c>
       <c r="D371" s="1">
-        <v>1296000</v>
+        <v>604800</v>
       </c>
       <c r="F371" s="2"/>
     </row>
@@ -7716,7 +7716,7 @@
         <v>2</v>
       </c>
       <c r="D372" s="1">
-        <v>1296000</v>
+        <v>604800</v>
       </c>
       <c r="F372" s="2"/>
     </row>
@@ -7732,7 +7732,7 @@
         <v>2</v>
       </c>
       <c r="D373" s="1">
-        <v>1296000</v>
+        <v>604800</v>
       </c>
       <c r="F373" s="2"/>
     </row>
@@ -7748,7 +7748,7 @@
         <v>2</v>
       </c>
       <c r="D374" s="1">
-        <v>1296000</v>
+        <v>604800</v>
       </c>
       <c r="F374" s="2"/>
     </row>

--- a/gu_in/ItemTimer.edf/TimerItem.xlsx
+++ b/gu_in/ItemTimer.edf/TimerItem.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA75358C-FFB6-4E3B-A451-9DEF8D55BDD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86CF29A0-D7A5-4377-A1FA-4C64337BB600}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1770" yWindow="1695" windowWidth="17565" windowHeight="11205" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TimerItem" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="567" uniqueCount="560">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="561">
   <si>
     <t>string[64]</t>
   </si>
@@ -1706,6 +1706,9 @@
   </si>
   <si>
     <t>irpre03</t>
+  </si>
+  <si>
+    <t>0.00000001157</t>
   </si>
 </sst>
 </file>
@@ -1754,10 +1757,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2101,8 +2105,7 @@
   <cols>
     <col min="1" max="2" width="9.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="16.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -10433,8 +10436,8 @@
       <c r="C553" s="1">
         <v>2</v>
       </c>
-      <c r="D553" s="1">
-        <v>86400</v>
+      <c r="D553" s="3" t="s">
+        <v>560</v>
       </c>
     </row>
     <row r="554" spans="1:4" x14ac:dyDescent="0.25">

--- a/gu_in/ItemTimer.edf/TimerItem.xlsx
+++ b/gu_in/ItemTimer.edf/TimerItem.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86CF29A0-D7A5-4377-A1FA-4C64337BB600}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD296092-915E-47BE-AE78-E805584507F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1770" yWindow="1695" windowWidth="17565" windowHeight="11205" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TimerItem" sheetId="1" r:id="rId1"/>
@@ -1780,9 +1780,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1820,9 +1820,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1855,26 +1855,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1907,26 +1890,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -10527,7 +10493,7 @@
         <v>2</v>
       </c>
       <c r="D559" s="1">
-        <v>1209600</v>
+        <v>604800</v>
       </c>
     </row>
     <row r="560" spans="1:4" x14ac:dyDescent="0.25">
